--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>724007</v>
+        <v>773885</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>786418</v>
+        <v>817553</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1755</v>
+        <v>1913</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179564</v>
+        <v>179506</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172833</v>
+        <v>172775</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162923</v>
+        <v>162865</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156969</v>
+        <v>156911</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153486</v>
+        <v>153428</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>149001</v>
+        <v>148943</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142499</v>
+        <v>142441</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139211</v>
+        <v>139153</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135363</v>
+        <v>135305</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124342</v>
+        <v>124284</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119759</v>
+        <v>119701</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>116141</v>
+        <v>116083</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115137</v>
+        <v>115079</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>110042</v>
+        <v>109984</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>101027</v>
+        <v>100969</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>97207</v>
+        <v>97149</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93604</v>
+        <v>93546</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93102</v>
+        <v>93044</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89530</v>
+        <v>89472</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88019</v>
+        <v>87961</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87854</v>
+        <v>87796</v>
       </c>
     </row>
     <row r="6">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>61</v>
@@ -6742,22 +6742,22 @@
         <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>41</v>
@@ -6772,7 +6772,7 @@
         <v>28</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>30</v>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.52</v>
+        <v>0.513</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1512180</v>
+        <v>1593351</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1755</v>
+        <v>1913</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 12, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 13, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>306331</v>
+        <v>309847</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4461</v>
+        <v>4497</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>10777</v>
+        <v>15014</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>146000</v>
+        <v>148213</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>77966</v>
+        <v>79323</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1034</v>
+        <v>1060</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53670</v>
+        <v>53780</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>509</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>25423</v>
+        <v>31838</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>21679</v>
+        <v>24518</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>347092</v>
+        <v>349153</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5277</v>
+        <v>5292</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>76945</v>
+        <v>77207</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9763,19 +9763,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Why Jalen Brunson Rejects the "King of NY" Title #Knicks #nba #basketball</t>
+          <t>Why Steve Nash Was Better to Play With Than LeBron James #nba #basketball</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>32611</v>
+        <v>34151</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>935</v>
+        <v>414</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9796,19 +9796,19 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
+          <t>Why Jalen Brunson Rejects the "King of NY" Title #Knicks #nba #basketball</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>31525</v>
+        <v>32674</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>644</v>
+        <v>937</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9829,19 +9829,19 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>CANNOT Believe This LeBron to Orlando Magic Take #nba #basketball #LebronJames</t>
+          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>29916</v>
+        <v>31548</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>430</v>
+        <v>644</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>773885</v>
+        <v>810951</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>817553</v>
+        <v>848154</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1913</v>
+        <v>2066</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179506</v>
+        <v>179455</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172775</v>
+        <v>172724</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162865</v>
+        <v>162814</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156911</v>
+        <v>156860</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153428</v>
+        <v>153377</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148943</v>
+        <v>148892</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142441</v>
+        <v>142390</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139153</v>
+        <v>139102</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135305</v>
+        <v>135254</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124284</v>
+        <v>124233</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119701</v>
+        <v>119650</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>116083</v>
+        <v>116032</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115079</v>
+        <v>115028</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109984</v>
+        <v>109933</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100969</v>
+        <v>100918</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>97149</v>
+        <v>97098</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93546</v>
+        <v>93495</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93044</v>
+        <v>92993</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89472</v>
+        <v>89421</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87961</v>
+        <v>87910</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87796</v>
+        <v>87745</v>
       </c>
     </row>
     <row r="6">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.513</v>
+        <v>0.511</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1593351</v>
+        <v>1661171</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1913</v>
+        <v>2066</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 13, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 14, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>309847</v>
+        <v>312677</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4497</v>
+        <v>4523</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15014</v>
+        <v>19047</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>148213</v>
+        <v>150939</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>943</v>
+        <v>962</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>79323</v>
+        <v>80830</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1060</v>
+        <v>1085</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53780</v>
+        <v>53857</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31838</v>
+        <v>36606</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>24518</v>
+        <v>25749</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>349153</v>
+        <v>351166</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5292</v>
+        <v>5321</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77207</v>
+        <v>77323</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>34151</v>
+        <v>37513</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32674</v>
+        <v>32743</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>937</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31548</v>
+        <v>31567</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>644</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>810951</v>
+        <v>839894</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>848154</v>
+        <v>889862</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2066</v>
+        <v>2206</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179455</v>
+        <v>179416</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172724</v>
+        <v>172685</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162814</v>
+        <v>162775</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156860</v>
+        <v>156821</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153377</v>
+        <v>153338</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148892</v>
+        <v>148853</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142390</v>
+        <v>142351</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139102</v>
+        <v>139063</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135254</v>
+        <v>135215</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124233</v>
+        <v>124194</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119650</v>
+        <v>119611</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>116032</v>
+        <v>115993</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115028</v>
+        <v>114989</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109933</v>
+        <v>109894</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100918</v>
+        <v>100879</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>97098</v>
+        <v>97059</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93495</v>
+        <v>93456</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92993</v>
+        <v>92954</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89421</v>
+        <v>89382</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87910</v>
+        <v>87871</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87745</v>
+        <v>87706</v>
       </c>
     </row>
     <row r="6">
@@ -6730,43 +6730,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>61</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>41</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>28</v>
@@ -6775,7 +6775,7 @@
         <v>35</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>21</v>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.511</v>
+        <v>0.514</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1661171</v>
+        <v>1731962</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2066</v>
+        <v>2206</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 14, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 15, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>312677</v>
+        <v>315316</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4523</v>
+        <v>4554</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>19047</v>
+        <v>20883</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>150939</v>
+        <v>152458</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>80830</v>
+        <v>82040</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1085</v>
+        <v>1108</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53857</v>
+        <v>53891</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>36606</v>
+        <v>38832</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>25749</v>
+        <v>26409</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>351166</v>
+        <v>352699</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5321</v>
+        <v>5337</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77323</v>
+        <v>77363</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>37513</v>
+        <v>38277</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32743</v>
+        <v>32780</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>937</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31567</v>
+        <v>31586</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>644</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>839894</v>
+        <v>864233</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>889862</v>
+        <v>917839</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2206</v>
+        <v>2386</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -6730,49 +6730,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1731962</v>
+        <v>1784458</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2206</v>
+        <v>2386</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 15, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 16, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>315316</v>
+        <v>317860</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4554</v>
+        <v>4580</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>20883</v>
+        <v>21909</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>152458</v>
+        <v>154732</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>82040</v>
+        <v>83626</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1108</v>
+        <v>1130</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53891</v>
+        <v>53911</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>511</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>38832</v>
+        <v>39977</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>26409</v>
+        <v>26785</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>352699</v>
+        <v>353693</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5337</v>
+        <v>5347</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77363</v>
+        <v>77408</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38277</v>
+        <v>38262</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32780</v>
+        <v>32830</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9838,10 +9838,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31586</v>
+        <v>31630</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>15</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>864233</v>
+        <v>881249</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>917839</v>
+        <v>941343</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2386</v>
+        <v>2520</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>15</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179416</v>
+        <v>179368</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172685</v>
+        <v>172637</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162775</v>
+        <v>162727</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156821</v>
+        <v>156773</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153338</v>
+        <v>153290</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148853</v>
+        <v>148805</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142351</v>
+        <v>142303</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139063</v>
+        <v>139015</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135215</v>
+        <v>135167</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124194</v>
+        <v>124146</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119611</v>
+        <v>119563</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115993</v>
+        <v>115945</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114989</v>
+        <v>114941</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109894</v>
+        <v>109846</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100879</v>
+        <v>100831</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>97059</v>
+        <v>97011</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93456</v>
+        <v>93408</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92954</v>
+        <v>92906</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89382</v>
+        <v>89334</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87871</v>
+        <v>87823</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87706</v>
+        <v>87658</v>
       </c>
     </row>
     <row r="6">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>64</v>
@@ -6739,22 +6739,22 @@
         <v>48</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>25</v>
@@ -6784,7 +6784,7 @@
         <v>11</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U8" s="7" t="n">
         <v>13</v>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.514</v>
+        <v>0.516</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1784458</v>
+        <v>1825112</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2386</v>
+        <v>2520</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 16, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 17, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>317860</v>
+        <v>320114</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4580</v>
+        <v>4558</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>21909</v>
+        <v>22305</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>154732</v>
+        <v>156691</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>83626</v>
+        <v>85503</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53911</v>
+        <v>53926</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>39977</v>
+        <v>40660</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>26785</v>
+        <v>27176</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>353693</v>
+        <v>354632</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5347</v>
+        <v>5339</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77408</v>
+        <v>77445</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38262</v>
+        <v>38421</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>455</v>
+        <v>242</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32830</v>
+        <v>32856</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31630</v>
+        <v>31676</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>881249</v>
+        <v>898017</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>941343</v>
+        <v>964055</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2520</v>
+        <v>2663</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179368</v>
+        <v>179355</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172637</v>
+        <v>172624</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162727</v>
+        <v>162714</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156773</v>
+        <v>156760</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153290</v>
+        <v>153277</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148805</v>
+        <v>148792</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142303</v>
+        <v>142290</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139015</v>
+        <v>139002</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135167</v>
+        <v>135154</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124146</v>
+        <v>124133</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119563</v>
+        <v>119550</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115945</v>
+        <v>115932</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114941</v>
+        <v>114928</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109846</v>
+        <v>109833</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100831</v>
+        <v>100818</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>97011</v>
+        <v>96998</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93408</v>
+        <v>93395</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92906</v>
+        <v>92893</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89334</v>
+        <v>89321</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87823</v>
+        <v>87810</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87658</v>
+        <v>87645</v>
       </c>
     </row>
     <row r="6">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.516</v>
+        <v>0.517</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1825112</v>
+        <v>1864735</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2520</v>
+        <v>2663</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 17, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 18, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>320114</v>
+        <v>322006</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4558</v>
+        <v>4618</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22305</v>
+        <v>22533</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>156691</v>
+        <v>158389</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>85503</v>
+        <v>86877</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1134</v>
+        <v>1167</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53926</v>
+        <v>53941</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>509</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>40660</v>
+        <v>41024</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27176</v>
+        <v>27294</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>354632</v>
+        <v>355427</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5339</v>
+        <v>5367</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77445</v>
+        <v>77493</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38421</v>
+        <v>38505</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>242</v>
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32856</v>
+        <v>32868</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>934</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31676</v>
+        <v>31687</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>898017</v>
+        <v>911899</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>964055</v>
+        <v>981777</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2663</v>
+        <v>2811</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5587,67 +5587,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179355</v>
+        <v>179347</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172624</v>
+        <v>172616</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162714</v>
+        <v>162706</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156760</v>
+        <v>156752</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153277</v>
+        <v>153269</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148792</v>
+        <v>148784</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142290</v>
+        <v>142282</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>139002</v>
+        <v>138994</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135154</v>
+        <v>135146</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124133</v>
+        <v>124125</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119550</v>
+        <v>119542</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115932</v>
+        <v>115924</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114928</v>
+        <v>114920</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109833</v>
+        <v>109825</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100818</v>
+        <v>100810</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96998</v>
+        <v>96990</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93395</v>
+        <v>93387</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92893</v>
+        <v>92885</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89321</v>
+        <v>89313</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87810</v>
+        <v>87802</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87645</v>
+        <v>87637</v>
       </c>
     </row>
     <row r="6">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>64</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>60</v>
@@ -6745,25 +6745,25 @@
         <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>22</v>
@@ -6772,19 +6772,19 @@
         <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>11</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U8" s="7" t="n">
         <v>13</v>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.517</v>
+        <v>0.518</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1864735</v>
+        <v>1896487</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2663</v>
+        <v>2811</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 18, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 19, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>322006</v>
+        <v>323985</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4618</v>
+        <v>4632</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22533</v>
+        <v>22656</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>229</v>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>158389</v>
+        <v>160621</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>86877</v>
+        <v>88472</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1167</v>
+        <v>1187</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53941</v>
+        <v>53956</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>41024</v>
+        <v>41261</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27294</v>
+        <v>27379</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>355427</v>
+        <v>355957</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5367</v>
+        <v>5374</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77493</v>
+        <v>77552</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38505</v>
+        <v>38564</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>242</v>
+        <v>454</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32868</v>
+        <v>32924</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31687</v>
+        <v>31730</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>911899</v>
+        <v>927346</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>981777</v>
+        <v>991560</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2811</v>
+        <v>2945</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5584,70 +5584,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>181000</v>
+        <v>179000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179347</v>
+        <v>177333</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172616</v>
+        <v>170602</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162706</v>
+        <v>160692</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156752</v>
+        <v>154738</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153269</v>
+        <v>151255</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148784</v>
+        <v>146770</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142282</v>
+        <v>140268</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138994</v>
+        <v>136980</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135146</v>
+        <v>133132</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124125</v>
+        <v>122111</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119542</v>
+        <v>117528</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115924</v>
+        <v>113910</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114920</v>
+        <v>112906</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109825</v>
+        <v>107811</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100810</v>
+        <v>98796</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96990</v>
+        <v>94976</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93387</v>
+        <v>91373</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92885</v>
+        <v>90871</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89313</v>
+        <v>87299</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87802</v>
+        <v>85788</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87637</v>
+        <v>85623</v>
       </c>
     </row>
     <row r="6">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.518</v>
+        <v>0.516</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1896487</v>
+        <v>1921851</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2811</v>
+        <v>2945</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 19, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 20, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>323985</v>
+        <v>325484</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4632</v>
+        <v>4646</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22656</v>
+        <v>22675</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>160621</v>
+        <v>161576</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>88472</v>
+        <v>89347</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1187</v>
+        <v>1210</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9585,19 +9585,19 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
+          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>53956</v>
+        <v>73808</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9618,19 +9618,19 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Paolo or Zion: Which NBA All-Star Gets TRADED First?</t>
+          <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>41261</v>
+        <v>53966</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>241</v>
+        <v>511</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9651,19 +9651,19 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Celtics #8, Orlando #10?! Perk’s BOLDEST Eastern Conference Predictions</t>
+          <t>Paolo or Zion: Which NBA All-Star Gets TRADED First?</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27379</v>
+        <v>41206</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>145</v>
+        <v>241</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>355957</v>
+        <v>356369</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5374</v>
+        <v>5385</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77552</v>
+        <v>77612</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38564</v>
+        <v>38568</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>454</v>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32924</v>
+        <v>32958</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31730</v>
+        <v>31755</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>927346</v>
+        <v>939201</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1419146</v>
+        <v>1271118</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1467445</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>991560</v>
+        <v>993459</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4512685</v>
+        <v>4186912</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>7373863</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2945</v>
+        <v>3044</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4620</v>
+        <v>4452</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>82434</v>
@@ -5584,70 +5584,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>179000</v>
+        <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>177333</v>
+        <v>179311</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>170602</v>
+        <v>172580</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>160692</v>
+        <v>162670</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>154738</v>
+        <v>156716</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>151255</v>
+        <v>153233</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>146770</v>
+        <v>148748</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>140268</v>
+        <v>142246</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>136980</v>
+        <v>138958</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>133132</v>
+        <v>135110</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>122111</v>
+        <v>124089</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>117528</v>
+        <v>119506</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>113910</v>
+        <v>115888</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>112906</v>
+        <v>114884</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>107811</v>
+        <v>109789</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>98796</v>
+        <v>100774</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>94976</v>
+        <v>96954</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>91373</v>
+        <v>93351</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>90871</v>
+        <v>92849</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>87299</v>
+        <v>89277</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>85788</v>
+        <v>87766</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>85623</v>
+        <v>87601</v>
       </c>
     </row>
     <row r="6">
@@ -6803,10 +6803,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.516</v>
+        <v>0.513</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.76</v>
+        <v>0.766</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.826</v>
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1921851</v>
+        <v>1935704</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5936451</v>
+        <v>5462482</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>8923742</v>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>2945</v>
+        <v>3044</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4620</v>
+        <v>4452</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>82434</v>
@@ -9372,7 +9372,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 20, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 21, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>325484</v>
+        <v>327093</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4646</v>
+        <v>4661</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22675</v>
+        <v>22760</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>161576</v>
+        <v>163713</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9552,19 +9552,19 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Jalen Brunson Explains Why 40 Focused Minutes Beat 2 Hours in the Gym</t>
+          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>89347</v>
+        <v>133087</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1210</v>
+        <v>873</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9585,19 +9585,19 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
+          <t>Jalen Brunson Explains Why 40 Focused Minutes Beat 2 Hours in the Gym</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>73808</v>
+        <v>90772</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>484</v>
+        <v>1231</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>53966</v>
+        <v>53981</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>511</v>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>41206</v>
+        <v>41210</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>356369</v>
+        <v>356931</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5385</v>
+        <v>5395</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77612</v>
+        <v>77669</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>1455</v>
@@ -9772,10 +9772,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38568</v>
+        <v>38572</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9805,10 +9805,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>32958</v>
+        <v>32985</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31755</v>
+        <v>31786</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -103,7 +103,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,7 +112,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -695,71 +695,115 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>5</v>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -987,10 +1031,8 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>7462</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>25874</v>
@@ -1090,91 +1132,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="9">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="9">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="9">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="9">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="9">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="9">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="9">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="9">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="9">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="9">
         <f>SUM(K5:K8)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="9">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="9">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="9">
         <f>SUM(N5:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="9">
         <f>SUM(O5:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="9">
         <f>SUM(P5:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="9">
         <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="9">
         <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="9">
         <f>SUM(S5:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="9">
         <f>SUM(T5:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="9">
         <f>SUM(U5:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="6">
+      <c r="V9" s="9">
         <f>SUM(V5:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="9">
         <f>SUM(W5:W8)</f>
         <v/>
       </c>
@@ -1387,71 +1429,115 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>5</v>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1460,96 +1546,112 @@
           <t>PER EP LISTENS</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>4136</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>5030</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>4091</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>4887</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>4774</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>4425</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>5522</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1561,96 +1663,94 @@
           <t>TOTAL LISTENS</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B6" s="9" t="n">
+        <v>12695</v>
+      </c>
+      <c r="C6" s="9" t="n">
         <v>62039</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="9" t="n">
         <v>60366</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="9" t="n">
         <v>65456</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>53760</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>62065</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>66378</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>49702</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1864,112 +1964,112 @@
           <t>VIEWS PER POST AVG</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1981,112 +2081,112 @@
           <t>TOTAL FOLLOWERS</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2449,112 +2549,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2566,112 +2666,112 @@
           <t>FOLLOWER GAIN (NET)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3034,112 +3134,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3151,112 +3251,112 @@
           <t xml:space="preserve">TOTAL POSTS </t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3619,112 +3719,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3736,112 +3836,112 @@
           <t>TOTAL VIEWS</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4204,112 +4304,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4321,112 +4421,112 @@
           <t>TOP POSTS</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4789,112 +4889,112 @@
           <t>ENGAGEMENT RATE</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5257,112 +5357,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5583,70 +5683,70 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="9" t="n">
         <v>181000</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="9" t="n">
         <v>179311</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="9" t="n">
         <v>172580</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="9" t="n">
         <v>162670</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>156716</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>153233</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>148748</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>142246</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="9" t="n">
         <v>138958</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>135110</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="9" t="n">
         <v>124089</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>119506</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="N5" s="9" t="n">
         <v>115888</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>114884</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="P5" s="9" t="n">
         <v>109789</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>100774</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="9" t="n">
         <v>96954</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>93351</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="T5" s="9" t="n">
         <v>92849</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>89277</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="V5" s="9" t="n">
         <v>87766</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="W5" s="9" t="n">
         <v>87601</v>
       </c>
     </row>
@@ -5993,91 +6093,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="9">
         <f>SUM(B8:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="9">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="9">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="9">
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="9">
         <f>SUM(F8:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="9">
         <f>SUM(G8:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="9">
         <f>SUM(H8:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="9">
         <f>SUM(I8:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="9">
         <f>SUM(J8:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="9">
         <f>SUM(K8:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="9">
         <f>SUM(L8:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="9">
         <f>SUM(M8:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="9">
         <f>SUM(N8:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="9">
         <f>SUM(O8:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="9">
         <f>SUM(P8:P9)</f>
         <v/>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="9">
         <f>SUM(Q8:Q9)</f>
         <v/>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="9">
         <f>SUM(R8:R9)</f>
         <v/>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="9">
         <f>SUM(S8:S9)</f>
         <v/>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="9">
         <f>SUM(T8:T9)</f>
         <v/>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="9">
         <f>SUM(U8:U9)</f>
         <v/>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="9">
         <f>SUM(V8:V9)</f>
         <v/>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="9">
         <f>SUM(W8:W9)</f>
         <v/>
       </c>
@@ -6184,91 +6284,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="9">
         <f>SUM(B5,B10)</f>
         <v/>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="9">
         <f>SUM(C5,C10)</f>
         <v/>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="9">
         <f>SUM(D5,D10)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="9">
         <f>SUM(E5,E10)</f>
         <v/>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="9">
         <f>SUM(F5,F10)</f>
         <v/>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="9">
         <f>SUM(G5,G10)</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="9">
         <f>SUM(H5,H10)</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="9">
         <f>SUM(I5,I10)</f>
         <v/>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="9">
         <f>SUM(J5,J10)</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="9">
         <f>SUM(K5,K10)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="9">
         <f>SUM(L5,L10)</f>
         <v/>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="9">
         <f>SUM(M5,M10)</f>
         <v/>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="9">
         <f>SUM(N5,N10)</f>
         <v/>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="9">
         <f>SUM(O5,O10)</f>
         <v/>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="9">
         <f>SUM(P5,P10)</f>
         <v/>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="9">
         <f>SUM(Q5,Q10)</f>
         <v/>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="9">
         <f>SUM(R5,R10)</f>
         <v/>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="9">
         <f>SUM(S5,S10)</f>
         <v/>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="9">
         <f>SUM(T5,T10)</f>
         <v/>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="9">
         <f>SUM(U5,U10)</f>
         <v/>
       </c>
-      <c r="V12" s="6">
+      <c r="V12" s="9">
         <f>SUM(V5,V10)</f>
         <v/>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="9">
         <f>SUM(W5,W10)</f>
         <v/>
       </c>
@@ -7676,112 +7776,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7793,112 +7893,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7910,112 +8010,112 @@
           <t>YOUTUBE</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8253,112 +8353,112 @@
           <t>LONG-FORM</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8482,112 +8582,112 @@
           <t>MID-FORM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8711,112 +8811,112 @@
           <t>SHORT-FORM</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8940,70 +9040,70 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="9" t="n">
         <v>1935704</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="9" t="n">
         <v>5462482</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="9" t="n">
         <v>8923742</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>4470139</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>2924880</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>3700890</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>3648573</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="9" t="n">
         <v>2078905</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>1845935</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="9" t="n">
         <v>2922473</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>2158005</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="9" t="n">
         <v>1494344</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>852234</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="9" t="n">
         <v>2645268</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>3546812</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="9" t="n">
         <v>1189839</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>764535</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="9" t="n">
         <v>212036</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>414323</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="9" t="n">
         <v>222611</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="9" t="n">
         <v>105674</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="9" t="n">
         <v>83412</v>
       </c>
     </row>
@@ -9036,112 +9136,112 @@
           <t>PER EP</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9153,70 +9253,70 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="9" t="n">
         <v>3044</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="9" t="n">
         <v>4452</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="9" t="n">
         <v>82434</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>169880</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>164514</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>178277</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>211738</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="9" t="n">
         <v>209927</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>90638</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>405</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="9" t="n">
         <v>381</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="9" t="n">
         <v>386</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>697</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="9" t="n">
         <v>37296</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>4972</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="9" t="n">
         <v>7173</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>1399</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="9" t="n">
         <v>78402</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="9" t="n">
         <v>3965</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="9" t="n">
         <v>11199</v>
       </c>
     </row>
@@ -9226,112 +9326,112 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9449,10 +9549,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>327093</v>
+        <v>327242</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4661</v>
+        <v>4662</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9481,10 +9581,10 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>22760</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="9" t="n">
+        <v>22771</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>230</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -9528,10 +9628,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>163713</v>
+        <v>163899</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9560,11 +9660,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>133087</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>873</v>
+      <c r="D10" s="9" t="n">
+        <v>136393</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>887</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9594,10 +9694,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>90772</v>
+        <v>90842</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9626,10 +9726,10 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="9" t="n">
         <v>53981</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="9" t="n">
         <v>511</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -9660,7 +9760,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>41210</v>
+        <v>41216</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9738,10 +9838,10 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>77669</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D17" s="9" t="n">
+        <v>77671</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>1455</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -9804,10 +9904,10 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>32985</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D19" s="9" t="n">
+        <v>32987</v>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>948</v>
       </c>
       <c r="F19" s="3" t="inlineStr">

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -103,7 +103,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,7 +112,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -695,115 +695,71 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -813,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>939201</v>
+        <v>1009191</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1271118</v>
@@ -886,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>993459</v>
+        <v>1005212</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4186912</v>
@@ -959,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3044</v>
+        <v>3302</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4452</v>
@@ -1132,91 +1088,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="6">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="6">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="6">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="6">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="6">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="6">
         <f>SUM(K5:K8)</f>
         <v/>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="6">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="6">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="6">
         <f>SUM(N5:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="6">
         <f>SUM(O5:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="6">
         <f>SUM(P5:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="6">
         <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="6">
         <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="6">
         <f>SUM(S5:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="9">
+      <c r="T9" s="6">
         <f>SUM(T5:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="9">
+      <c r="U9" s="6">
         <f>SUM(U5:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="9">
+      <c r="V9" s="6">
         <f>SUM(V5:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="9">
+      <c r="W9" s="6">
         <f>SUM(W5:W8)</f>
         <v/>
       </c>
@@ -1429,115 +1385,71 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" s="6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1546,112 +1458,94 @@
           <t>PER EP LISTENS</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="B5" s="6" t="n">
+        <v>4232</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4136</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5030</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4091</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4887</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>4774</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>4425</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>5522</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1663,94 +1557,94 @@
           <t>TOTAL LISTENS</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="6" t="n">
         <v>12695</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="6" t="n">
         <v>62039</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="6" t="n">
         <v>60366</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="6" t="n">
         <v>65456</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="6" t="n">
         <v>53760</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="6" t="n">
         <v>62065</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="6" t="n">
         <v>66378</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="6" t="n">
         <v>49702</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1964,112 +1858,112 @@
           <t>VIEWS PER POST AVG</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2081,112 +1975,112 @@
           <t>TOTAL FOLLOWERS</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2549,112 +2443,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="6" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2666,112 +2560,112 @@
           <t>FOLLOWER GAIN (NET)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="6" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3134,112 +3028,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3251,112 +3145,112 @@
           <t xml:space="preserve">TOTAL POSTS </t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3719,112 +3613,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3836,112 +3730,112 @@
           <t>TOTAL VIEWS</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W20" s="6" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4304,112 +4198,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W24" s="6" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4421,112 +4315,112 @@
           <t>TOP POSTS</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V25" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W25" s="6" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V25" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4889,112 +4783,112 @@
           <t>ENGAGEMENT RATE</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V29" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W29" s="6" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V29" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5357,112 +5251,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W33" s="6" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V33" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5683,71 +5577,71 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="6" t="n">
         <v>181000</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>179311</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>172580</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>162670</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>156716</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>153233</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>148748</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>142246</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>138958</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>135110</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>124089</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>119506</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>115888</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>114884</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>109789</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>100774</v>
-      </c>
-      <c r="R5" s="9" t="n">
-        <v>96954</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>93351</v>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v>92849</v>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>89277</v>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v>87766</v>
-      </c>
-      <c r="W5" s="9" t="n">
-        <v>87601</v>
+      <c r="C5" s="6" t="n">
+        <v>179231</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>172500</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>162590</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>156636</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>153153</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>148668</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>142166</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>138878</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>135030</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>124009</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>119426</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>115808</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>114804</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>109709</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>100694</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>96874</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>93271</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>92769</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>89197</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>87686</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>87521</v>
       </c>
     </row>
     <row r="6">
@@ -6093,91 +5987,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="6">
         <f>SUM(B8:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="6">
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <f>SUM(F8:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="6">
         <f>SUM(G8:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="6">
         <f>SUM(H8:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="6">
         <f>SUM(I8:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="6">
         <f>SUM(J8:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="6">
         <f>SUM(K8:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="6">
         <f>SUM(L8:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="6">
         <f>SUM(M8:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="6">
         <f>SUM(N8:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="6">
         <f>SUM(O8:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="6">
         <f>SUM(P8:P9)</f>
         <v/>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="6">
         <f>SUM(Q8:Q9)</f>
         <v/>
       </c>
-      <c r="R10" s="9">
+      <c r="R10" s="6">
         <f>SUM(R8:R9)</f>
         <v/>
       </c>
-      <c r="S10" s="9">
+      <c r="S10" s="6">
         <f>SUM(S8:S9)</f>
         <v/>
       </c>
-      <c r="T10" s="9">
+      <c r="T10" s="6">
         <f>SUM(T8:T9)</f>
         <v/>
       </c>
-      <c r="U10" s="9">
+      <c r="U10" s="6">
         <f>SUM(U8:U9)</f>
         <v/>
       </c>
-      <c r="V10" s="9">
+      <c r="V10" s="6">
         <f>SUM(V8:V9)</f>
         <v/>
       </c>
-      <c r="W10" s="9">
+      <c r="W10" s="6">
         <f>SUM(W8:W9)</f>
         <v/>
       </c>
@@ -6284,91 +6178,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <f>SUM(B5,B10)</f>
         <v/>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <f>SUM(C5,C10)</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <f>SUM(D5,D10)</f>
         <v/>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="6">
         <f>SUM(E5,E10)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <f>SUM(F5,F10)</f>
         <v/>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="6">
         <f>SUM(G5,G10)</f>
         <v/>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="6">
         <f>SUM(H5,H10)</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="6">
         <f>SUM(I5,I10)</f>
         <v/>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="6">
         <f>SUM(J5,J10)</f>
         <v/>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="6">
         <f>SUM(K5,K10)</f>
         <v/>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="6">
         <f>SUM(L5,L10)</f>
         <v/>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="6">
         <f>SUM(M5,M10)</f>
         <v/>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="6">
         <f>SUM(N5,N10)</f>
         <v/>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="6">
         <f>SUM(O5,O10)</f>
         <v/>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="6">
         <f>SUM(P5,P10)</f>
         <v/>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="6">
         <f>SUM(Q5,Q10)</f>
         <v/>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="6">
         <f>SUM(R5,R10)</f>
         <v/>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="6">
         <f>SUM(S5,S10)</f>
         <v/>
       </c>
-      <c r="T12" s="9">
+      <c r="T12" s="6">
         <f>SUM(T5,T10)</f>
         <v/>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="6">
         <f>SUM(U5,U10)</f>
         <v/>
       </c>
-      <c r="V12" s="9">
+      <c r="V12" s="6">
         <f>SUM(V5,V10)</f>
         <v/>
       </c>
-      <c r="W12" s="9">
+      <c r="W12" s="6">
         <f>SUM(W5,W10)</f>
         <v/>
       </c>
@@ -6830,49 +6724,49 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="L8" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="M8" s="7" t="n">
+      <c r="O8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="N8" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>27</v>
-      </c>
       <c r="P8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
@@ -6903,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.513</v>
+        <v>0.498</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.766</v>
@@ -7776,112 +7670,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7893,112 +7787,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8010,112 +7904,112 @@
           <t>YOUTUBE</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8353,112 +8247,112 @@
           <t>LONG-FORM</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X5" s="6" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8582,112 +8476,112 @@
           <t>MID-FORM</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X7" s="6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X7" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8811,112 +8705,112 @@
           <t>SHORT-FORM</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X9" s="6" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X9" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9040,70 +8934,70 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>1935704</v>
-      </c>
-      <c r="D11" s="9" t="n">
+      <c r="C11" s="6" t="n">
+        <v>2017705</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>5462482</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="6" t="n">
         <v>8923742</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="6" t="n">
         <v>4470139</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="6" t="n">
         <v>2924880</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="6" t="n">
         <v>3700890</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="6" t="n">
         <v>3648573</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="6" t="n">
         <v>2078905</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="6" t="n">
         <v>1845935</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="6" t="n">
         <v>2922473</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="6" t="n">
         <v>2158005</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="6" t="n">
         <v>1494344</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" s="6" t="n">
         <v>852234</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" s="6" t="n">
         <v>2645268</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="6" t="n">
         <v>3546812</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="6" t="n">
         <v>1189839</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="6" t="n">
         <v>764535</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="6" t="n">
         <v>212036</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" s="6" t="n">
         <v>414323</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="6" t="n">
         <v>222611</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="6" t="n">
         <v>105674</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="6" t="n">
         <v>83412</v>
       </c>
     </row>
@@ -9136,112 +9030,112 @@
           <t>PER EP</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X13" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9253,70 +9147,70 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>3044</v>
-      </c>
-      <c r="D14" s="9" t="n">
+      <c r="C14" s="6" t="n">
+        <v>3302</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>4452</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="6" t="n">
         <v>82434</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="6" t="n">
         <v>169880</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="6" t="n">
         <v>164514</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="6" t="n">
         <v>178277</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="6" t="n">
         <v>211738</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="6" t="n">
         <v>209927</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="6" t="n">
         <v>90638</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="6" t="n">
         <v>365</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="6" t="n">
         <v>405</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="N14" s="6" t="n">
         <v>381</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="6" t="n">
         <v>386</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="6" t="n">
         <v>697</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="6" t="n">
         <v>37296</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="6" t="n">
         <v>4972</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="6" t="n">
         <v>7173</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="6" t="n">
         <v>1399</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="6" t="n">
         <v>78402</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="6" t="n">
         <v>3965</v>
       </c>
-      <c r="X14" s="9" t="n">
+      <c r="X14" s="6" t="n">
         <v>11199</v>
       </c>
     </row>
@@ -9326,112 +9220,112 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X15" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9472,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 21, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 22, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9549,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>327242</v>
+        <v>328717</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4662</v>
+        <v>4674</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9581,10 +9475,10 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>22771</v>
-      </c>
-      <c r="E6" s="9" t="n">
+      <c r="D6" s="6" t="n">
+        <v>22846</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>230</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -9628,10 +9522,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>163899</v>
+        <v>165151</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9660,11 +9554,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>136393</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>887</v>
+      <c r="D10" s="6" t="n">
+        <v>163758</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1031</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9694,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>90842</v>
+        <v>91760</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1233</v>
+        <v>1248</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9726,10 +9620,10 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>53981</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="D12" s="6" t="n">
+        <v>53988</v>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>511</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -9760,7 +9654,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>41216</v>
+        <v>41285</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9806,10 +9700,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>356931</v>
+        <v>357884</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5395</v>
+        <v>5404</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9838,11 +9732,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>77671</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>1455</v>
+      <c r="D17" s="6" t="n">
+        <v>77719</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1456</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9872,7 +9766,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38572</v>
+        <v>38599</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>455</v>
@@ -9904,10 +9798,10 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>32987</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="6" t="n">
+        <v>33013</v>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>948</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -9938,7 +9832,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31786</v>
+        <v>31798</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1009191</v>
+        <v>1093253</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1271118</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1005212</v>
+        <v>1010794</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4186912</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3302</v>
+        <v>3631</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4452</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179231</v>
+        <v>179168</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172500</v>
+        <v>172437</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162590</v>
+        <v>162527</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156636</v>
+        <v>156573</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153153</v>
+        <v>153090</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148668</v>
+        <v>148605</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142166</v>
+        <v>142103</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138878</v>
+        <v>138815</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>135030</v>
+        <v>134967</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>124009</v>
+        <v>123946</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119426</v>
+        <v>119363</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115808</v>
+        <v>115745</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114804</v>
+        <v>114741</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109709</v>
+        <v>109646</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100694</v>
+        <v>100631</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96874</v>
+        <v>96811</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93271</v>
+        <v>93208</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92769</v>
+        <v>92706</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89197</v>
+        <v>89134</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87686</v>
+        <v>87623</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87521</v>
+        <v>87458</v>
       </c>
     </row>
     <row r="6">
@@ -6724,55 +6724,55 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>40</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>23</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>11</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.498</v>
+        <v>0.48</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.766</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2017705</v>
+        <v>2107678</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5462482</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3302</v>
+        <v>3631</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4452</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 22, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 23, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>328717</v>
+        <v>330463</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4674</v>
+        <v>4685</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22846</v>
+        <v>22878</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9513,19 +9513,19 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>Jalen Brunson Breaks Down How the Knicks ATTACKED Wemby</t>
+          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>165151</v>
+        <v>194102</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1048</v>
+        <v>1156</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9546,19 +9546,19 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
+          <t>Jalen Brunson Breaks Down How the Knicks ATTACKED Wemby</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>163758</v>
+        <v>166259</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1031</v>
+        <v>1053</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>91760</v>
+        <v>92970</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1248</v>
+        <v>1264</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>53988</v>
+        <v>54000</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>511</v>
@@ -9645,19 +9645,19 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Paolo or Zion: Which NBA All-Star Gets TRADED First?</t>
+          <t>“One-on-One Is Not Basketball” — Richard Jefferson Explains Why</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>41285</v>
+        <v>42513</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>241</v>
+        <v>431</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>357884</v>
+        <v>359446</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5404</v>
+        <v>5427</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>77719</v>
+        <v>77776</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>38599</v>
+        <v>38612</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>455</v>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>33013</v>
+        <v>33033</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>948</v>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>31798</v>
+        <v>31806</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>645</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>15</v>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1093253</v>
+        <v>1152951</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1271118</v>
+        <v>1419146</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1467445</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1010794</v>
+        <v>1019632</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4186912</v>
+        <v>4512685</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>7373863</v>
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3631</v>
+        <v>3880</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4452</v>
+        <v>4620</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>82434</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>15</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4232</v>
+        <v>3174</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>4136</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179168</v>
+        <v>179109</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172437</v>
+        <v>172378</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162527</v>
+        <v>162468</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156573</v>
+        <v>156514</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153090</v>
+        <v>153031</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148605</v>
+        <v>148546</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142103</v>
+        <v>142044</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138815</v>
+        <v>138756</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134967</v>
+        <v>134908</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123946</v>
+        <v>123887</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119363</v>
+        <v>119304</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115745</v>
+        <v>115686</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114741</v>
+        <v>114682</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109646</v>
+        <v>109587</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100631</v>
+        <v>100572</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96811</v>
+        <v>96752</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93208</v>
+        <v>93149</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92706</v>
+        <v>92647</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89134</v>
+        <v>89075</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87623</v>
+        <v>87564</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87458</v>
+        <v>87399</v>
       </c>
     </row>
     <row r="6">
@@ -6724,22 +6724,22 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>55</v>
@@ -6748,7 +6748,7 @@
         <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>23</v>
@@ -6760,16 +6760,16 @@
         <v>31</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>21</v>
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.48</v>
+        <v>0.468</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.766</v>
+        <v>0.76</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.826</v>
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2107678</v>
+        <v>2176463</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5462482</v>
+        <v>5936451</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>8923742</v>
@@ -9148,10 +9148,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3631</v>
+        <v>3880</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>4452</v>
+        <v>4620</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>82434</v>
@@ -9351,7 +9351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 23, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 24, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>330463</v>
+        <v>331906</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4685</v>
+        <v>4696</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22878</v>
+        <v>22905</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9492,364 +9492,397 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>CM 9 17 26 LONG v2 1</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>194102</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1156</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D10" s="7" t="n">
+        <v>211601</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Jalen Brunson Breaks Down How the Knicks ATTACKED Wemby</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>166259</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>1053</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D11" s="6" t="n">
+        <v>166977</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Jalen Brunson Explains Why 40 Focused Minutes Beat 2 Hours in the Gym</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>92970</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1264</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D12" s="7" t="n">
+        <v>93772</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>54000</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="D13" s="6" t="n">
+        <v>54030</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>511</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>“One-on-One Is Not Basketball” — Richard Jefferson Explains Why</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>42513</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>431</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D14" s="7" t="n">
+        <v>49536</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Jalen Brunson’s HONEST Reaction to  New Look Philadelphia 76ers #nba #basketball #lebronjames</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>359446</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>5427</v>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="D17" s="7" t="n">
+        <v>360396</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>5441</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>“She Has To Raise 3 Kids…” Jalen Brunson EXPOSES Josh Hart #nba #basketball #JalenBrunson #Knicks</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>77776</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D18" s="6" t="n">
+        <v>77844</v>
+      </c>
+      <c r="E18" s="6" t="n">
         <v>1457</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Why Steve Nash Was Better to Play With Than LeBron James #nba #basketball</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>38612</v>
-      </c>
-      <c r="E18" s="7" t="n">
+      <c r="D19" s="7" t="n">
+        <v>38622</v>
+      </c>
+      <c r="E19" s="7" t="n">
         <v>455</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Why Jalen Brunson Rejects the "King of NY" Title #Knicks #nba #basketball</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>33033</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D20" s="6" t="n">
+        <v>33060</v>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>948</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
-        <v>31806</v>
-      </c>
-      <c r="E20" s="7" t="n">
+      <c r="D21" s="7" t="n">
+        <v>31811</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>645</v>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9857,8 +9890,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>331906</v>
+        <v>331954</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4696</v>
+        <v>4697</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>211601</v>
+        <v>212521</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1240</v>
+        <v>1249</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>166977</v>
+        <v>167062</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>1054</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>93772</v>
+        <v>93774</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>1274</v>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>49536</v>
+        <v>49795</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>77844</v>
+        <v>77848</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38622</v>
+        <v>38626</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>455</v>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33060</v>
+        <v>33061</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1152951</v>
+        <v>1202886</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1019632</v>
+        <v>1049283</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3880</v>
+        <v>4078</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179109</v>
+        <v>179045</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172378</v>
+        <v>172314</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162468</v>
+        <v>162404</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156514</v>
+        <v>156450</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>153031</v>
+        <v>152967</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148546</v>
+        <v>148482</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>142044</v>
+        <v>141980</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138756</v>
+        <v>138692</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134908</v>
+        <v>134844</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123887</v>
+        <v>123823</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119304</v>
+        <v>119240</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115686</v>
+        <v>115622</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114682</v>
+        <v>114618</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109587</v>
+        <v>109523</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100572</v>
+        <v>100508</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96752</v>
+        <v>96688</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93149</v>
+        <v>93085</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92647</v>
+        <v>92583</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89075</v>
+        <v>89011</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87564</v>
+        <v>87500</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87399</v>
+        <v>87335</v>
       </c>
     </row>
     <row r="6">
@@ -6733,22 +6733,22 @@
         <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>23</v>
@@ -6763,7 +6763,7 @@
         <v>24</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>36</v>
@@ -6784,7 +6784,7 @@
         <v>13</v>
       </c>
       <c r="V8" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W8" s="7" t="n">
         <v>2</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.468</v>
+        <v>0.465</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2176463</v>
+        <v>2256247</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3880</v>
+        <v>4078</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 24, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 25, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>331954</v>
+        <v>333206</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4697</v>
+        <v>4707</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22905</v>
+        <v>22921</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>212521</v>
+        <v>232398</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1249</v>
+        <v>1329</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>167062</v>
+        <v>167907</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>93774</v>
+        <v>94554</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9645,19 +9645,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
+          <t>“One-on-One Is Not Basketball” — Richard Jefferson Explains Why</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>54030</v>
+        <v>54308</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9678,19 +9678,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>“One-on-One Is Not Basketball” — Richard Jefferson Explains Why</t>
+          <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>49795</v>
+        <v>54039</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>360396</v>
+        <v>361103</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5441</v>
+        <v>5446</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>77848</v>
+        <v>77908</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38626</v>
+        <v>38645</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>455</v>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33061</v>
+        <v>33105</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9856,19 +9856,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
+          <t>CANNOT Believe This LeBron to Orlando Magic Take #nba #basketball #LebronJames</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>31811</v>
+        <v>30875</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>645</v>
+        <v>438</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1202886</v>
+        <v>1243865</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1049283</v>
+        <v>1069403</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4078</v>
+        <v>4220</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179045</v>
+        <v>179007</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172314</v>
+        <v>172276</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162404</v>
+        <v>162366</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156450</v>
+        <v>156412</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>152967</v>
+        <v>152929</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148482</v>
+        <v>148444</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>141980</v>
+        <v>141942</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138692</v>
+        <v>138654</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134844</v>
+        <v>134806</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123823</v>
+        <v>123785</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119240</v>
+        <v>119202</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115622</v>
+        <v>115584</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114618</v>
+        <v>114580</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109523</v>
+        <v>109485</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100508</v>
+        <v>100470</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96688</v>
+        <v>96650</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93085</v>
+        <v>93047</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92583</v>
+        <v>92545</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>89011</v>
+        <v>88973</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87500</v>
+        <v>87462</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87335</v>
+        <v>87297</v>
       </c>
     </row>
     <row r="6">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>49</v>
@@ -6736,7 +6736,7 @@
         <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>57</v>
@@ -6745,34 +6745,34 @@
         <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>38</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>11</v>
@@ -6784,7 +6784,7 @@
         <v>13</v>
       </c>
       <c r="V8" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W8" s="7" t="n">
         <v>2</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.465</v>
+        <v>0.461</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2256247</v>
+        <v>2317488</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4078</v>
+        <v>4220</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 25, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 26, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>333206</v>
+        <v>334499</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4707</v>
+        <v>4723</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22921</v>
+        <v>22936</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9500,19 +9500,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>CM 9 17 26 LONG v2 1</t>
+          <t>Greg Oden Didn’t Expect To Be The No. 1 Pick</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1</v>
+        <v>3186</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>232398</v>
+        <v>243610</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1329</v>
+        <v>1376</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>167907</v>
+        <v>168498</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>94554</v>
+        <v>95031</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>54308</v>
+        <v>59530</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>523</v>
+        <v>585</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>54039</v>
+        <v>54047</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>511</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>361103</v>
+        <v>361931</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5446</v>
+        <v>5459</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>77908</v>
+        <v>77967</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38645</v>
+        <v>38668</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>455</v>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33105</v>
+        <v>33144</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9856,19 +9856,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>CANNOT Believe This LeBron to Orlando Magic Take #nba #basketball #LebronJames</t>
+          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>30875</v>
+        <v>31861</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>438</v>
+        <v>646</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1243865</v>
+        <v>1288322</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1069403</v>
+        <v>1085448</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4220</v>
+        <v>4407</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>179007</v>
+        <v>178948</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172276</v>
+        <v>172217</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162366</v>
+        <v>162307</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156412</v>
+        <v>156353</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>152929</v>
+        <v>152870</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148444</v>
+        <v>148385</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>141942</v>
+        <v>141883</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138654</v>
+        <v>138595</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134806</v>
+        <v>134747</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123785</v>
+        <v>123726</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119202</v>
+        <v>119143</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115584</v>
+        <v>115525</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114580</v>
+        <v>114521</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109485</v>
+        <v>109426</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100470</v>
+        <v>100411</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96650</v>
+        <v>96591</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>93047</v>
+        <v>92988</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92545</v>
+        <v>92486</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88973</v>
+        <v>88914</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87462</v>
+        <v>87403</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87297</v>
+        <v>87238</v>
       </c>
     </row>
     <row r="6">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>49</v>
@@ -6736,25 +6736,25 @@
         <v>57</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <v>57</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>34</v>
       </c>
       <c r="J8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="n">
         <v>38</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>39</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>30</v>
@@ -6766,7 +6766,7 @@
         <v>27</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.461</v>
+        <v>0.456</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2317488</v>
+        <v>2378177</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4220</v>
+        <v>4407</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 26, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 27, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>334499</v>
+        <v>335701</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4723</v>
+        <v>4731</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22936</v>
+        <v>22951</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3186</v>
+        <v>4063</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>243610</v>
+        <v>251783</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1376</v>
+        <v>1408</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>168498</v>
+        <v>169204</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>95031</v>
+        <v>95357</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>59530</v>
+        <v>64835</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>585</v>
+        <v>646</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>54047</v>
+        <v>54052</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>511</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>361931</v>
+        <v>362562</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5459</v>
+        <v>5470</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>77967</v>
+        <v>78010</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1460</v>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38668</v>
+        <v>38694</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33144</v>
+        <v>33169</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>31861</v>
+        <v>31871</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>646</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1288322</v>
+        <v>1322250</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1085448</v>
+        <v>1108958</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4407</v>
+        <v>4535</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>178948</v>
+        <v>178913</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172217</v>
+        <v>172182</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162307</v>
+        <v>162272</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156353</v>
+        <v>156318</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>152870</v>
+        <v>152835</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148385</v>
+        <v>148350</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>141883</v>
+        <v>141848</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138595</v>
+        <v>138560</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134747</v>
+        <v>134712</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123726</v>
+        <v>123691</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119143</v>
+        <v>119108</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115525</v>
+        <v>115490</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114521</v>
+        <v>114486</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109426</v>
+        <v>109391</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100411</v>
+        <v>100376</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96591</v>
+        <v>96556</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92988</v>
+        <v>92953</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92486</v>
+        <v>92451</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88914</v>
+        <v>88879</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87403</v>
+        <v>87368</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87238</v>
+        <v>87203</v>
       </c>
     </row>
     <row r="6">
@@ -6727,46 +6727,46 @@
         <v>34</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>56</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>31</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.76</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2378177</v>
+        <v>2435743</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4407</v>
+        <v>4535</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 27, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 28, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>335701</v>
+        <v>337031</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4731</v>
+        <v>4748</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22951</v>
+        <v>22958</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4063</v>
+        <v>5329</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>251783</v>
+        <v>256813</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1408</v>
+        <v>1432</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>169204</v>
+        <v>169887</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>95357</v>
+        <v>95722</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1290</v>
+        <v>1301</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>64835</v>
+        <v>68696</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>646</v>
+        <v>688</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>54052</v>
+        <v>54068</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>362562</v>
+        <v>363137</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5470</v>
+        <v>5476</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78010</v>
+        <v>78052</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38694</v>
+        <v>38727</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33169</v>
+        <v>33237</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>31871</v>
+        <v>31886</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>646</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1322250</v>
+        <v>1347495</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1108958</v>
+        <v>1127052</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4535</v>
+        <v>4660</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>178913</v>
+        <v>178882</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172182</v>
+        <v>172151</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162272</v>
+        <v>162241</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156318</v>
+        <v>156287</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>152835</v>
+        <v>152804</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148350</v>
+        <v>148319</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>141848</v>
+        <v>141817</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138560</v>
+        <v>138529</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134712</v>
+        <v>134681</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123691</v>
+        <v>123660</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119108</v>
+        <v>119077</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115490</v>
+        <v>115459</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114486</v>
+        <v>114455</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109391</v>
+        <v>109360</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100376</v>
+        <v>100345</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96556</v>
+        <v>96525</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92953</v>
+        <v>92922</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92451</v>
+        <v>92420</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88879</v>
+        <v>88848</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87368</v>
+        <v>87337</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87203</v>
+        <v>87172</v>
       </c>
     </row>
     <row r="6">
@@ -6730,13 +6730,13 @@
         <v>64</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>56</v>
@@ -6745,10 +6745,10 @@
         <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>26</v>
@@ -6772,7 +6772,7 @@
         <v>31</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>11</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2435743</v>
+        <v>2479207</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4535</v>
+        <v>4660</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 28, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 29, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>337031</v>
+        <v>338012</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4748</v>
+        <v>4753</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22958</v>
+        <v>22965</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>5329</v>
+        <v>6058</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>256813</v>
+        <v>260900</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1432</v>
+        <v>1455</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>169887</v>
+        <v>170466</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>95722</v>
+        <v>95883</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>68696</v>
+        <v>71372</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>688</v>
+        <v>721</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>54068</v>
+        <v>54069</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>512</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>363137</v>
+        <v>364134</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5476</v>
+        <v>5490</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78052</v>
+        <v>78086</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38727</v>
+        <v>38742</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>458</v>
@@ -9823,19 +9823,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Why Jalen Brunson Rejects the "King of NY" Title #Knicks #nba #basketball</t>
+          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33237</v>
+        <v>31923</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>957</v>
+        <v>646</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9856,19 +9856,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
+          <t>“Straight Garbage.” 💀 Channing Frye ROASTS the Brooklyn Nets #nba #basketball #michaelporterjr</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>31886</v>
+        <v>31063</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>646</v>
+        <v>469</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>1347495</v>
+        <v>1366001</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1127052</v>
+        <v>1143670</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>4512685</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>4660</v>
+        <v>4774</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>4620</v>
@@ -5581,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>178882</v>
+        <v>178856</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>172151</v>
+        <v>172125</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>162241</v>
+        <v>162215</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>156287</v>
+        <v>156261</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>152804</v>
+        <v>152778</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>148319</v>
+        <v>148293</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>141817</v>
+        <v>141791</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>138529</v>
+        <v>138503</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>134681</v>
+        <v>134655</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>123660</v>
+        <v>123634</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>119077</v>
+        <v>119051</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>115459</v>
+        <v>115433</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>114455</v>
+        <v>114429</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>109360</v>
+        <v>109334</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>100345</v>
+        <v>100319</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>96525</v>
+        <v>96499</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>92922</v>
+        <v>92896</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92420</v>
+        <v>92394</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>88848</v>
+        <v>88822</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>87337</v>
+        <v>87311</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87172</v>
+        <v>87146</v>
       </c>
     </row>
     <row r="6">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>2479207</v>
+        <v>2514445</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>5936451</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>4660</v>
+        <v>4774</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4620</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 29, 2026</t>
+          <t>⭐ BEST OF — Sep 01 – Sep 30, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>338012</v>
+        <v>338952</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4753</v>
+        <v>4756</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>22965</v>
+        <v>22970</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>230</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6058</v>
+        <v>6657</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>260900</v>
+        <v>265631</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1455</v>
+        <v>1467</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>170466</v>
+        <v>171096</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>95883</v>
+        <v>96010</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>71372</v>
+        <v>74971</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>54069</v>
+        <v>54074</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>512</v>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>364134</v>
+        <v>365387</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>5490</v>
+        <v>5509</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78086</v>
+        <v>78113</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1462</v>
@@ -9799,10 +9799,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>38742</v>
+        <v>38759</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>31923</v>
+        <v>31948</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>31063</v>
+        <v>31122</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>469</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -103,16 +103,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -128,15 +128,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -580,112 +571,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -695,70 +686,72 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="V4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -768,71 +761,73 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>1366001</v>
-      </c>
-      <c r="C5" s="7" t="n">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1385463</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>1419146</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="E5" s="9" t="n">
         <v>1467445</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="F5" s="9" t="n">
         <v>983168</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="G5" s="9" t="n">
         <v>697914</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="9" t="n">
         <v>790809</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="I5" s="9" t="n">
         <v>999377</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="J5" s="9" t="n">
         <v>456937</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="K5" s="9" t="n">
         <v>733899</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="L5" s="9" t="n">
         <v>1819209</v>
       </c>
-      <c r="L5" s="7" t="n">
+      <c r="M5" s="9" t="n">
         <v>1237011</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="9" t="n">
         <v>951387</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="O5" s="9" t="n">
         <v>461276</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="P5" s="9" t="n">
         <v>1296821</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="Q5" s="9" t="n">
         <v>1515762</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="R5" s="9" t="n">
         <v>606682</v>
       </c>
-      <c r="R5" s="7" t="n">
+      <c r="S5" s="9" t="n">
         <v>629557</v>
       </c>
-      <c r="S5" s="7" t="n">
+      <c r="T5" s="9" t="n">
         <v>115398</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="U5" s="9" t="n">
         <v>322450</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="V5" s="9" t="n">
         <v>87239</v>
       </c>
-      <c r="V5" s="7" t="n">
+      <c r="W5" s="9" t="n">
         <v>67472</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>48198</v>
       </c>
     </row>
     <row r="6">
@@ -841,71 +836,73 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>1143670</v>
-      </c>
-      <c r="C6" s="7" t="n">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1158698</v>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>4512685</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="9" t="n">
         <v>7373863</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="F6" s="9" t="n">
         <v>3317091</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="G6" s="9" t="n">
         <v>2062452</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="H6" s="9" t="n">
         <v>2731804</v>
       </c>
-      <c r="H6" s="7" t="n">
+      <c r="I6" s="9" t="n">
         <v>2437458</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="J6" s="9" t="n">
         <v>1412041</v>
       </c>
-      <c r="J6" s="7" t="n">
+      <c r="K6" s="9" t="n">
         <v>1021398</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="L6" s="9" t="n">
         <v>1102899</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="M6" s="9" t="n">
         <v>920589</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="9" t="n">
         <v>542576</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="O6" s="9" t="n">
         <v>390738</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="P6" s="9" t="n">
         <v>1348061</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="Q6" s="9" t="n">
         <v>2030353</v>
       </c>
-      <c r="Q6" s="7" t="n">
+      <c r="R6" s="9" t="n">
         <v>545861</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="S6" s="9" t="n">
         <v>130006</v>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="T6" s="9" t="n">
         <v>89465</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="U6" s="9" t="n">
         <v>90474</v>
       </c>
-      <c r="U6" s="7" t="n">
+      <c r="V6" s="9" t="n">
         <v>56970</v>
       </c>
-      <c r="V6" s="7" t="n">
+      <c r="W6" s="9" t="n">
         <v>34237</v>
-      </c>
-      <c r="W6" s="7" t="n">
-        <v>24015</v>
       </c>
     </row>
     <row r="7">
@@ -914,71 +911,73 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>4774</v>
-      </c>
-      <c r="C7" s="7" t="n">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>4858</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>4620</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>82434</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="F7" s="9" t="n">
         <v>169880</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="G7" s="9" t="n">
         <v>164514</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="9" t="n">
         <v>178277</v>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="I7" s="9" t="n">
         <v>211738</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="J7" s="9" t="n">
         <v>209927</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="K7" s="9" t="n">
         <v>90638</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="L7" s="9" t="n">
         <v>365</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="M7" s="9" t="n">
         <v>405</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="9" t="n">
         <v>381</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="O7" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="P7" s="9" t="n">
         <v>386</v>
       </c>
-      <c r="P7" s="7" t="n">
+      <c r="Q7" s="9" t="n">
         <v>697</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="R7" s="9" t="n">
         <v>37296</v>
       </c>
-      <c r="R7" s="7" t="n">
+      <c r="S7" s="9" t="n">
         <v>4972</v>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="T7" s="9" t="n">
         <v>7173</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="U7" s="9" t="n">
         <v>1399</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="V7" s="9" t="n">
         <v>78402</v>
       </c>
-      <c r="V7" s="7" t="n">
+      <c r="W7" s="9" t="n">
         <v>3965</v>
-      </c>
-      <c r="W7" s="7" t="n">
-        <v>11199</v>
       </c>
     </row>
     <row r="8">
@@ -987,34 +986,34 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>7462</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <v>25874</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="9" t="n">
         <v>25231</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="9" t="n">
         <v>23305</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="9" t="n">
         <v>23182</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="9" t="n">
         <v>25288</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>24712</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="J8" s="9" t="n">
         <v>22848</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
@@ -1088,91 +1087,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <f>SUM(I5:I8)</f>
         <v/>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="7">
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="7">
         <f>SUM(K5:K8)</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <f>SUM(L5:L8)</f>
         <v/>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="7">
         <f>SUM(M5:M8)</f>
         <v/>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="7">
         <f>SUM(N5:N8)</f>
         <v/>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="7">
         <f>SUM(O5:O8)</f>
         <v/>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="7">
         <f>SUM(P5:P8)</f>
         <v/>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="7">
         <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="7">
         <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="7">
         <f>SUM(S5:S8)</f>
         <v/>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="7">
         <f>SUM(T5:T8)</f>
         <v/>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="7">
         <f>SUM(U5:U8)</f>
         <v/>
       </c>
-      <c r="V9" s="6">
+      <c r="V9" s="7">
         <f>SUM(V5:V8)</f>
         <v/>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="7">
         <f>SUM(W5:W8)</f>
         <v/>
       </c>
@@ -1270,112 +1269,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -1385,70 +1384,72 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="P4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="R4" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="V4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" s="6" t="n">
+      <c r="W4" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1458,94 +1459,94 @@
           <t>PER EP LISTENS</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>3174</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>4136</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>5030</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>4091</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>4887</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>4774</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>4425</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="7" t="n">
         <v>5522</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1557,94 +1558,94 @@
           <t>TOTAL LISTENS</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>12695</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>62039</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>60366</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>65456</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>53760</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>62065</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>66378</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="7" t="n">
         <v>49702</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1743,112 +1744,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -1858,112 +1859,112 @@
           <t>VIEWS PER POST AVG</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1975,112 +1976,112 @@
           <t>TOTAL FOLLOWERS</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2443,112 +2444,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2560,112 +2561,112 @@
           <t>FOLLOWER GAIN (NET)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3028,112 +3029,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3145,112 +3146,112 @@
           <t xml:space="preserve">TOTAL POSTS </t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3613,112 +3614,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V19" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3730,112 +3731,112 @@
           <t>TOTAL VIEWS</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4198,112 +4199,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4315,112 +4316,112 @@
           <t>TOP POSTS</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4783,112 +4784,112 @@
           <t>ENGAGEMENT RATE</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W29" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5251,112 +5252,112 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W33" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5455,112 +5456,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -5577,71 +5578,71 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>181000</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>178856</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>172125</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>162215</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>156261</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>152778</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>148293</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>141791</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>138503</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>134655</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>123634</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>119051</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>115433</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>114429</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>109334</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>100319</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>96499</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>92896</v>
-      </c>
-      <c r="T5" s="6" t="n">
-        <v>92394</v>
-      </c>
-      <c r="U5" s="6" t="n">
-        <v>88822</v>
-      </c>
-      <c r="V5" s="6" t="n">
-        <v>87311</v>
-      </c>
-      <c r="W5" s="6" t="n">
-        <v>87146</v>
+      <c r="C5" s="7" t="n">
+        <v>181000</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>178822</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>172091</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>162181</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>156227</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>152744</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>148259</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>141757</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>138469</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>134621</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>123600</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>119017</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>115399</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>114395</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>109300</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>100285</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>96465</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>92862</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>92360</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>88788</v>
+      </c>
+      <c r="W5" s="7" t="n">
+        <v>87277</v>
       </c>
     </row>
     <row r="6">
@@ -5650,87 +5651,87 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="9">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="9">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="9">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="9">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="9">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="9">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="9">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="9">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="7">
+      <c r="T6" s="9">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="9">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="7">
+      <c r="V6" s="9">
         <f>V5-W5</f>
         <v/>
       </c>
@@ -5987,91 +5988,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <f>SUM(B8:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <f>SUM(C8:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <f>SUM(D8:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <f>SUM(E8:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>SUM(F8:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <f>SUM(G8:G9)</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <f>SUM(H8:H9)</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <f>SUM(I8:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="7">
         <f>SUM(J8:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="7">
         <f>SUM(K8:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <f>SUM(L8:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="7">
         <f>SUM(M8:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="7">
         <f>SUM(N8:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="7">
         <f>SUM(O8:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="7">
         <f>SUM(P8:P9)</f>
         <v/>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="7">
         <f>SUM(Q8:Q9)</f>
         <v/>
       </c>
-      <c r="R10" s="6">
+      <c r="R10" s="7">
         <f>SUM(R8:R9)</f>
         <v/>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="7">
         <f>SUM(S8:S9)</f>
         <v/>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="7">
         <f>SUM(T8:T9)</f>
         <v/>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="7">
         <f>SUM(U8:U9)</f>
         <v/>
       </c>
-      <c r="V10" s="6">
+      <c r="V10" s="7">
         <f>SUM(V8:V9)</f>
         <v/>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="7">
         <f>SUM(W8:W9)</f>
         <v/>
       </c>
@@ -6082,87 +6083,87 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="9">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="9">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="9">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="9">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="9">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="9">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="9">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="9">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="9">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="9">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="9">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="9">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="9">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="9">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="9">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="9">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="9">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="9">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="9">
         <f>V10-W10</f>
         <v/>
       </c>
@@ -6178,91 +6179,91 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <f>SUM(B5,B10)</f>
         <v/>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <f>SUM(C5,C10)</f>
         <v/>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <f>SUM(D5,D10)</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>SUM(E5,E10)</f>
         <v/>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <f>SUM(F5,F10)</f>
         <v/>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="7">
         <f>SUM(G5,G10)</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="7">
         <f>SUM(H5,H10)</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="7">
         <f>SUM(I5,I10)</f>
         <v/>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="7">
         <f>SUM(J5,J10)</f>
         <v/>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="7">
         <f>SUM(K5,K10)</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="7">
         <f>SUM(L5,L10)</f>
         <v/>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="7">
         <f>SUM(M5,M10)</f>
         <v/>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="7">
         <f>SUM(N5,N10)</f>
         <v/>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="7">
         <f>SUM(O5,O10)</f>
         <v/>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="7">
         <f>SUM(P5,P10)</f>
         <v/>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="7">
         <f>SUM(Q5,Q10)</f>
         <v/>
       </c>
-      <c r="R12" s="6">
+      <c r="R12" s="7">
         <f>SUM(R5,R10)</f>
         <v/>
       </c>
-      <c r="S12" s="6">
+      <c r="S12" s="7">
         <f>SUM(S5,S10)</f>
         <v/>
       </c>
-      <c r="T12" s="6">
+      <c r="T12" s="7">
         <f>SUM(T5,T10)</f>
         <v/>
       </c>
-      <c r="U12" s="6">
+      <c r="U12" s="7">
         <f>SUM(U5,U10)</f>
         <v/>
       </c>
-      <c r="V12" s="6">
+      <c r="V12" s="7">
         <f>SUM(V5,V10)</f>
         <v/>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="7">
         <f>SUM(W5,W10)</f>
         <v/>
       </c>
@@ -6360,112 +6361,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -6723,71 +6724,73 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="D8" s="9" t="n">
         <v>64</v>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="E8" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="F8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="I8" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="J8" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="K8" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="K8" s="7" t="n">
+      <c r="L8" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="M8" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="N8" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="O8" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="P8" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="P8" s="7" t="n">
+      <c r="Q8" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="Q8" s="7" t="n">
+      <c r="R8" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R8" s="7" t="n">
+      <c r="S8" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="S8" s="7" t="n">
+      <c r="T8" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="U8" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="U8" s="7" t="n">
+      <c r="V8" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="V8" s="7" t="n">
+      <c r="W8" s="9" t="n">
         <v>14</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6796,71 +6799,73 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>0.455</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.76</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.826</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.742</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.705</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.738</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="I9" s="12" t="n">
         <v>0.668</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="J9" s="12" t="n">
         <v>0.679</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="K9" s="12" t="n">
         <v>0.553</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="L9" s="12" t="n">
         <v>0.377</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="M9" s="12" t="n">
         <v>0.427</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="N9" s="12" t="n">
         <v>0.363</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="O9" s="12" t="n">
         <v>0.458</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="P9" s="12" t="n">
         <v>0.51</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="Q9" s="12" t="n">
         <v>0.572</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="R9" s="12" t="n">
         <v>0.459</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="S9" s="12" t="n">
         <v>0.17</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="T9" s="12" t="n">
         <v>0.422</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="U9" s="12" t="n">
         <v>0.218</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="V9" s="12" t="n">
         <v>0.256</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="W9" s="12" t="n">
         <v>0.324</v>
-      </c>
-      <c r="W9" s="12" t="n">
-        <v>0.288</v>
       </c>
     </row>
     <row r="10">
@@ -7555,112 +7560,112 @@
     <row r="3">
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -7670,112 +7675,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7787,112 +7792,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7904,112 +7909,112 @@
           <t>YOUTUBE</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8109,112 +8114,112 @@
     <row r="3">
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>OCT</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>SEP</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>DEC 25</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>NOV 25</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>OCT 25</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>SEP 25</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>AUG 25</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>JUL 25</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>JUN 25</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>MAY 25</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>APR 25</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>MAR 25</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>FEB 25</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>JAN 25</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>DEC 24</t>
         </is>
       </c>
     </row>
@@ -8247,112 +8252,112 @@
           <t>LONG-FORM</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8476,112 +8481,112 @@
           <t>MID-FORM</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8705,112 +8710,112 @@
           <t>SHORT-FORM</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8934,71 +8939,73 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>2514445</v>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2549019</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>5936451</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>8923742</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>4470139</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>2924880</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>3700890</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>3648573</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>2078905</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>1845935</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>2922473</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>2158005</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>1494344</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>852234</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>2645268</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>3546812</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>1189839</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>764535</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>212036</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>414323</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>222611</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>105674</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>83412</v>
       </c>
     </row>
     <row r="12">
@@ -9030,112 +9037,112 @@
           <t>PER EP</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9147,71 +9154,73 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>4774</v>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>4858</v>
+      </c>
+      <c r="E14" s="7" t="n">
         <v>4620</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>82434</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>169880</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>164514</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>178277</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>211738</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>209927</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>90638</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>365</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>381</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>386</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>697</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>37296</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>4972</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>7173</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>1399</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>78402</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>3965</v>
-      </c>
-      <c r="X14" s="6" t="n">
-        <v>11199</v>
       </c>
     </row>
     <row r="15">
@@ -9220,112 +9229,112 @@
           <t># OF EPS</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9351,7 +9360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9366,7 +9375,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Sep 01 – Sep 30, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 01, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9426,463 +9435,55 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>Jalen Brunson Never Planned On Being a Star</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>338952</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>4756</v>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>LeBron Is Philly’s THIRD-BEST Player... and Could Retire If It Fails</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>22970</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>230</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Greg Oden Didn’t Expect To Be The No. 1 Pick</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>6657</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>LONG</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>“Two Words All Day” — MPJ Describes Cam Thomas at Practice</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>265631</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Jalen Brunson Breaks Down How the Knicks ATTACKED Wemby</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>171096</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1088</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Jalen Brunson Explains Why 40 Focused Minutes Beat 2 Hours in the Gym</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>96010</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>1309</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>“One-on-One Is Not Basketball” — Richard Jefferson Explains Why</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>74971</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>768</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Kawhi Set the Clippers Back 15 Years - Perk Called It LAST YEAR</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>54074</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>512</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Jalen Brunson’s HONEST Reaction to  New Look Philadelphia 76ers #nba #basketball #lebronjames</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>365387</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>5509</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>“She Has To Raise 3 Kids…” Jalen Brunson EXPOSES Josh Hart #nba #basketball #JalenBrunson #Knicks</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>78113</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1462</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Why Steve Nash Was Better to Play With Than LeBron James #nba #basketball</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>38759</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>459</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Kendrick Perkins CRAZIEST All-Star Prediction Yet?! #nba #basketball #bostonceltics</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>31948</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>647</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>“Straight Garbage.” 💀 Channing Frye ROASTS the Brooklyn Nets #nba #basketball #michaelporterjr</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>31122</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>469</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9890,9 +9491,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>1385463</v>
+        <v>1405303</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>1419146</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1158698</v>
+        <v>1166893</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>4512685</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4858</v>
+        <v>4934</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4620</v>
@@ -5585,64 +5585,64 @@
         <v>181000</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>178822</v>
+        <v>178791</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>172091</v>
+        <v>172060</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>162181</v>
+        <v>162150</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>156227</v>
+        <v>156196</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>152744</v>
+        <v>152713</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>148259</v>
+        <v>148228</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>141757</v>
+        <v>141726</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>138469</v>
+        <v>138438</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>134621</v>
+        <v>134590</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>123600</v>
+        <v>123569</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>119017</v>
+        <v>118986</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>115399</v>
+        <v>115368</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>114395</v>
+        <v>114364</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>109300</v>
+        <v>109269</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>100285</v>
+        <v>100254</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>96465</v>
+        <v>96434</v>
       </c>
       <c r="T5" s="7" t="n">
-        <v>92862</v>
+        <v>92831</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>92360</v>
+        <v>92329</v>
       </c>
       <c r="V5" s="7" t="n">
-        <v>88788</v>
+        <v>88757</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>87277</v>
+        <v>87246</v>
       </c>
     </row>
     <row r="6">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0.76</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2549019</v>
+        <v>2577130</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>5936451</v>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>4858</v>
+        <v>4934</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>4620</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +130,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6724,16 +6730,14 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B8" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>34</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>49</v>
@@ -6742,16 +6746,16 @@
         <v>56</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>55</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>36</v>
@@ -6763,7 +6767,7 @@
         <v>37</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>25</v>
@@ -6772,7 +6776,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R8" s="9" t="n">
         <v>31</v>
@@ -9375,7 +9379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 01, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 02, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,10 +9479,36 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>No data for this period</t>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>2645</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -106,10 +106,10 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -765,72 +765,70 @@
           <t>YT VIDS</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>1422054</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="B5" s="7" t="n">
+        <v>12708</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>1422041</v>
+      </c>
+      <c r="D5" s="7" t="n">
         <v>1419146</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <v>1467445</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="7" t="n">
         <v>983168</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <v>697914</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="7" t="n">
         <v>790809</v>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="I5" s="7" t="n">
         <v>999377</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="7" t="n">
         <v>456937</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="K5" s="7" t="n">
         <v>733899</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="7" t="n">
         <v>1819209</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="7" t="n">
         <v>1237011</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="7" t="n">
         <v>951387</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="7" t="n">
         <v>461276</v>
       </c>
-      <c r="P5" s="8" t="n">
+      <c r="P5" s="7" t="n">
         <v>1296821</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="7" t="n">
         <v>1515762</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="7" t="n">
         <v>606682</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="7" t="n">
         <v>629557</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="7" t="n">
         <v>115398</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="7" t="n">
         <v>322450</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="7" t="n">
         <v>87239</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="7" t="n">
         <v>67472</v>
       </c>
     </row>
@@ -840,72 +838,70 @@
           <t>YT SHORTS</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1172879</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="B6" s="7" t="n">
+        <v>6843</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1172865</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>4512685</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>7373863</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="7" t="n">
         <v>3317091</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="G6" s="7" t="n">
         <v>2062452</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="7" t="n">
         <v>2731804</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="7" t="n">
         <v>2437458</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="7" t="n">
         <v>1412041</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="K6" s="7" t="n">
         <v>1021398</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="7" t="n">
         <v>1102899</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="7" t="n">
         <v>920589</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="7" t="n">
         <v>542576</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="O6" s="7" t="n">
         <v>390738</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="P6" s="7" t="n">
         <v>1348061</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="7" t="n">
         <v>2030353</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="7" t="n">
         <v>545861</v>
       </c>
-      <c r="S6" s="8" t="n">
+      <c r="S6" s="7" t="n">
         <v>130006</v>
       </c>
-      <c r="T6" s="8" t="n">
+      <c r="T6" s="7" t="n">
         <v>89465</v>
       </c>
-      <c r="U6" s="8" t="n">
+      <c r="U6" s="7" t="n">
         <v>90474</v>
       </c>
-      <c r="V6" s="8" t="n">
+      <c r="V6" s="7" t="n">
         <v>56970</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="7" t="n">
         <v>34237</v>
       </c>
     </row>
@@ -915,72 +911,70 @@
           <t>YT LIVES</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>5023</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="B7" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>5022</v>
+      </c>
+      <c r="D7" s="7" t="n">
         <v>4620</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>82434</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="7" t="n">
         <v>169880</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="7" t="n">
         <v>164514</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="7" t="n">
         <v>178277</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="7" t="n">
         <v>211738</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="7" t="n">
         <v>209927</v>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="K7" s="7" t="n">
         <v>90638</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="L7" s="7" t="n">
         <v>365</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="7" t="n">
         <v>405</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="7" t="n">
         <v>381</v>
       </c>
-      <c r="O7" s="8" t="n">
+      <c r="O7" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="P7" s="7" t="n">
         <v>386</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="7" t="n">
         <v>697</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="7" t="n">
         <v>37296</v>
       </c>
-      <c r="S7" s="8" t="n">
+      <c r="S7" s="7" t="n">
         <v>4972</v>
       </c>
-      <c r="T7" s="8" t="n">
+      <c r="T7" s="7" t="n">
         <v>7173</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="7" t="n">
         <v>1399</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="7" t="n">
         <v>78402</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="7" t="n">
         <v>3965</v>
       </c>
     </row>
@@ -990,96 +984,96 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
         <v>7462</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>25874</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>25231</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>23305</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>23182</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>25288</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>24712</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="7" t="n">
         <v>22848</v>
       </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2095,112 +2089,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2212,112 +2206,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2329,112 +2323,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2680,112 +2674,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2797,112 +2791,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2914,112 +2908,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3265,112 +3259,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W16" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3382,112 +3376,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3499,112 +3493,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3850,112 +3844,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W21" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3967,112 +3961,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4084,112 +4078,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V23" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4435,112 +4429,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V26" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W26" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4552,112 +4546,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V27" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4669,112 +4663,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V28" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4903,112 +4897,112 @@
           <t>INSTAGRAM</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V30" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5020,112 +5014,112 @@
           <t>TWITTER/X</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V31" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5137,112 +5131,112 @@
           <t>TIKTOK</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W32" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5584,67 +5578,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181000</v>
+        <v>180968</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178764</v>
+        <v>178732</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172033</v>
+        <v>172001</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162123</v>
+        <v>162091</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156169</v>
+        <v>156137</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152686</v>
+        <v>152654</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148201</v>
+        <v>148169</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141699</v>
+        <v>141667</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138411</v>
+        <v>138379</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134563</v>
+        <v>134531</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123542</v>
+        <v>123510</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118959</v>
+        <v>118927</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115341</v>
+        <v>115309</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114337</v>
+        <v>114305</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109242</v>
+        <v>109210</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100227</v>
+        <v>100195</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96407</v>
+        <v>96375</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92804</v>
+        <v>92772</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92302</v>
+        <v>92270</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88730</v>
+        <v>88698</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87219</v>
+        <v>87187</v>
       </c>
     </row>
     <row r="6">
@@ -5653,91 +5647,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>F5-G5</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>G5-H5</f>
         <v/>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>I5-J5</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>J5-K5</f>
         <v/>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>K5-L5</f>
         <v/>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>L5-M5</f>
         <v/>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>M5-N5</f>
         <v/>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>N5-O5</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>O5-P5</f>
         <v/>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f>P5-Q5</f>
         <v/>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <f>Q5-R5</f>
         <v/>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <f>R5-S5</f>
         <v/>
       </c>
-      <c r="S6" s="8">
+      <c r="S6" s="7">
         <f>S5-T5</f>
         <v/>
       </c>
-      <c r="T6" s="8">
+      <c r="T6" s="7">
         <f>T5-U5</f>
         <v/>
       </c>
-      <c r="U6" s="8">
+      <c r="U6" s="7">
         <f>U5-V5</f>
         <v/>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="7">
         <f>V5-W5</f>
         <v/>
       </c>
-      <c r="W6" s="7" t="inlineStr">
+      <c r="W6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5756,112 +5750,112 @@
           <t>APPLE</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5873,112 +5867,112 @@
           <t>SPOTIFY</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6085,91 +6079,91 @@
           <t>(+/-)</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <f>F10-G10</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <f>G10-H10</f>
         <v/>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <f>K10-L10</f>
         <v/>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <f>L10-M10</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <f>M10-N10</f>
         <v/>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <f>N10-O10</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="7">
         <f>O10-P10</f>
         <v/>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f>P10-Q10</f>
         <v/>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="7">
         <f>Q10-R10</f>
         <v/>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <f>R10-S10</f>
         <v/>
       </c>
-      <c r="S11" s="8">
+      <c r="S11" s="7">
         <f>S10-T10</f>
         <v/>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="7">
         <f>T10-U10</f>
         <v/>
       </c>
-      <c r="U11" s="8">
+      <c r="U11" s="7">
         <f>U10-V10</f>
         <v/>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="7">
         <f>V10-W10</f>
         <v/>
       </c>
-      <c r="W11" s="7" t="inlineStr">
+      <c r="W11" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6726,70 +6720,70 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="K8" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="L8" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="N8" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="O8" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="P8" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="Q8" s="8" t="n">
+      <c r="Q8" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="T8" s="8" t="n">
+      <c r="T8" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="V8" s="8" t="n">
+      <c r="V8" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6799,10 +6793,8 @@
           <t>% OF VIEWS</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B9" s="12" t="n">
+        <v>0.348</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8364,112 +8356,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8593,112 +8585,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8822,112 +8814,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8939,13 +8931,11 @@
           <t>TOTAL PACKAGE</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C11" s="6" t="n">
+        <v>19646</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2599956</v>
+        <v>2599928</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>5936451</v>
@@ -9154,13 +9144,11 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="C14" s="6" t="n">
+        <v>95</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5023</v>
+        <v>5022</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4620</v>
@@ -9375,7 +9363,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 03, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 04, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9471,10 +9459,10 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -9517,11 +9505,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>4693</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>104</v>
+      <c r="D11" s="7" t="n">
+        <v>5552</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>12708</v>
+        <v>25411</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1422041</v>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>6843</v>
+        <v>14176</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172865</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5022</v>
@@ -5578,67 +5578,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180968</v>
+        <v>180951</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178732</v>
+        <v>178715</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172001</v>
+        <v>171984</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162091</v>
+        <v>162074</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156137</v>
+        <v>156120</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152654</v>
+        <v>152637</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148169</v>
+        <v>148152</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141667</v>
+        <v>141650</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138379</v>
+        <v>138362</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134531</v>
+        <v>134514</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123510</v>
+        <v>123493</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118927</v>
+        <v>118910</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115309</v>
+        <v>115292</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114305</v>
+        <v>114288</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109210</v>
+        <v>109193</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100195</v>
+        <v>100178</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96375</v>
+        <v>96358</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92772</v>
+        <v>92755</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92270</v>
+        <v>92253</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88698</v>
+        <v>88681</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87187</v>
+        <v>87170</v>
       </c>
     </row>
     <row r="6">
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.348</v>
+        <v>0.357</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>19646</v>
+        <v>39754</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2599928</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5022</v>
@@ -9363,7 +9363,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 04, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 05, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5552</v>
+        <v>6084</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6084</v>
+        <v>6128</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>25411</v>
+        <v>38073</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1422041</v>
+        <v>1419833</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1419146</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14176</v>
+        <v>21005</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1172865</v>
+        <v>1172108</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>4512685</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5022</v>
+        <v>5016</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>4620</v>
@@ -5578,67 +5578,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180951</v>
+        <v>180932</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178715</v>
+        <v>178696</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171984</v>
+        <v>171965</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162074</v>
+        <v>162055</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156120</v>
+        <v>156101</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152637</v>
+        <v>152618</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148152</v>
+        <v>148133</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141650</v>
+        <v>141631</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138362</v>
+        <v>138343</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134514</v>
+        <v>134495</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123493</v>
+        <v>123474</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118910</v>
+        <v>118891</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115292</v>
+        <v>115273</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114288</v>
+        <v>114269</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109193</v>
+        <v>109174</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100178</v>
+        <v>100159</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96358</v>
+        <v>96339</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92755</v>
+        <v>92736</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92253</v>
+        <v>92234</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88681</v>
+        <v>88662</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87170</v>
+        <v>87151</v>
       </c>
     </row>
     <row r="6">
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8932,10 +8932,10 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>39754</v>
+        <v>59315</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2599928</v>
+        <v>2596957</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>5936451</v>
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>167</v>
+        <v>237</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5022</v>
+        <v>5016</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4620</v>
@@ -9363,7 +9363,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 05, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 06, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6128</v>
+        <v>6339</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>38073</v>
+        <v>54185</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>21005</v>
+        <v>25827</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5578,67 +5578,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180932</v>
+        <v>180906</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178696</v>
+        <v>178670</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171965</v>
+        <v>171939</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162055</v>
+        <v>162029</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156101</v>
+        <v>156075</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152618</v>
+        <v>152592</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148133</v>
+        <v>148107</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141631</v>
+        <v>141605</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138343</v>
+        <v>138317</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134495</v>
+        <v>134469</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123474</v>
+        <v>123448</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118891</v>
+        <v>118865</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115273</v>
+        <v>115247</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114269</v>
+        <v>114243</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109174</v>
+        <v>109148</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100159</v>
+        <v>100133</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96339</v>
+        <v>96313</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92736</v>
+        <v>92710</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92234</v>
+        <v>92208</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88662</v>
+        <v>88636</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87151</v>
+        <v>87125</v>
       </c>
     </row>
     <row r="6">
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.354</v>
+        <v>0.321</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8932,7 +8932,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>59315</v>
+        <v>80338</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9363,7 +9363,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 06, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 07, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6339</v>
+        <v>6381</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>129</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,12 +130,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -766,7 +760,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>54185</v>
+        <v>67527</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -839,7 +833,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>25827</v>
+        <v>30089</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -912,7 +906,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>326</v>
+        <v>466</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5578,67 +5572,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180906</v>
+        <v>180888</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178670</v>
+        <v>178652</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171939</v>
+        <v>171921</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162029</v>
+        <v>162011</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156075</v>
+        <v>156057</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152592</v>
+        <v>152574</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148107</v>
+        <v>148089</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141605</v>
+        <v>141587</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138317</v>
+        <v>138299</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134469</v>
+        <v>134451</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123448</v>
+        <v>123430</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118865</v>
+        <v>118847</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115247</v>
+        <v>115229</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114243</v>
+        <v>114225</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109148</v>
+        <v>109130</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100133</v>
+        <v>100115</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96313</v>
+        <v>96295</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92710</v>
+        <v>92692</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92208</v>
+        <v>92190</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88636</v>
+        <v>88618</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87125</v>
+        <v>87107</v>
       </c>
     </row>
     <row r="6">
@@ -6720,71 +6714,115 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="V8" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W8" s="7" t="n">
-        <v>14</v>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6794,7 +6832,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.321</v>
+        <v>0.307</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8932,7 +8970,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>80338</v>
+        <v>98082</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9145,7 +9183,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>326</v>
+        <v>466</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9363,7 +9401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 07, 2026</t>
+          <t>⭐ BEST OF — Oct 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9443,36 +9481,10 @@
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="14" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>Why Miami Will Be a HUGE Adjustment for Giannis + Ja Morant Needed a Change of Scenery</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>GROUP</t>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
         </is>
       </c>
     </row>
@@ -9489,36 +9501,10 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>6381</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>129</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>GROUP</t>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>No data for this period</t>
         </is>
       </c>
     </row>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -130,6 +130,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>67527</v>
+        <v>79888</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -833,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>30089</v>
+        <v>34351</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -906,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>466</v>
+        <v>556</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5572,67 +5581,67 @@
         <v>181000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180888</v>
+        <v>180875</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178652</v>
+        <v>178639</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171921</v>
+        <v>171908</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162011</v>
+        <v>161998</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156057</v>
+        <v>156044</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152574</v>
+        <v>152561</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148089</v>
+        <v>148076</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141587</v>
+        <v>141574</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138299</v>
+        <v>138286</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134451</v>
+        <v>134438</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123430</v>
+        <v>123417</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118847</v>
+        <v>118834</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115229</v>
+        <v>115216</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114225</v>
+        <v>114212</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109130</v>
+        <v>109117</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100115</v>
+        <v>100102</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96295</v>
+        <v>96282</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92692</v>
+        <v>92679</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92190</v>
+        <v>92177</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88618</v>
+        <v>88605</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87107</v>
+        <v>87094</v>
       </c>
     </row>
     <row r="6">
@@ -6714,115 +6723,71 @@
           <t># OF SHORTS</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W8" s="7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -6832,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.307</v>
+        <v>0.299</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8970,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>98082</v>
+        <v>114795</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9183,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>466</v>
+        <v>556</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9386,7 +9351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9401,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 09, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9481,10 +9446,36 @@
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="14" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>No data for this period</t>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Why Miami Will Be a HUGE Adjustment for Giannis + Ja Morant Needed a Change of Scenery</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>
@@ -9501,15 +9492,107 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="14" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>No data for this period</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>31273</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>547</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>5318</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>35</v>
@@ -6736,31 +6736,31 @@
         <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>23</v>
@@ -6769,7 +6769,7 @@
         <v>29</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>31</v>
@@ -9351,7 +9351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9454,19 +9454,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Why Miami Will Be a HUGE Adjustment for Giannis + Ja Morant Needed a Change of Scenery</t>
+          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>31273</v>
+        <v>31487</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6500</v>
+        <v>6505</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>131</v>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5318</v>
+        <v>5888</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9591,8 +9591,41 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2289</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>79888</v>
+        <v>89661</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>34351</v>
+        <v>63832</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5578,70 +5578,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>181000</v>
+        <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>180875</v>
+        <v>181871</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178639</v>
+        <v>179635</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>171908</v>
+        <v>172904</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>161998</v>
+        <v>162994</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156044</v>
+        <v>157040</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152561</v>
+        <v>153557</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148076</v>
+        <v>149072</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141574</v>
+        <v>142570</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138286</v>
+        <v>139282</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134438</v>
+        <v>135434</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123417</v>
+        <v>124413</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118834</v>
+        <v>119830</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115216</v>
+        <v>116212</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114212</v>
+        <v>115208</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109117</v>
+        <v>110113</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100102</v>
+        <v>101098</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96282</v>
+        <v>97278</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92679</v>
+        <v>93675</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92177</v>
+        <v>93173</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88605</v>
+        <v>89601</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87094</v>
+        <v>88090</v>
       </c>
     </row>
     <row r="6">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>64</v>
@@ -6736,25 +6736,25 @@
         <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>53</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>32</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>37</v>
@@ -6766,13 +6766,13 @@
         <v>23</v>
       </c>
       <c r="P8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="R8" s="7" t="n">
         <v>29</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="R8" s="7" t="n">
-        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.299</v>
+        <v>0.414</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>114795</v>
+        <v>154105</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9351,7 +9351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 09, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 10, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>221</v>
+        <v>3444</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9500,19 +9500,19 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>31487</v>
+        <v>47925</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>548</v>
+        <v>1129</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9533,19 +9533,19 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6505</v>
+        <v>32100</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>131</v>
+        <v>563</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5888</v>
+        <v>9933</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9599,19 +9599,19 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
+          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2289</v>
+        <v>6582</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9624,8 +9624,41 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>3761</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>117</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>47925</v>
+        <v>50399</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1129</v>
+        <v>1202</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32100</v>
+        <v>32141</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>9933</v>
+        <v>10302</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6582</v>
+        <v>6589</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>135</v>
@@ -9641,10 +9641,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3761</v>
+        <v>4544</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>89661</v>
+        <v>98614</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>63832</v>
+        <v>77719</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5581,67 +5581,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181871</v>
+        <v>181848</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179635</v>
+        <v>179612</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172904</v>
+        <v>172881</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162994</v>
+        <v>162971</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>157040</v>
+        <v>157017</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153557</v>
+        <v>153534</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149072</v>
+        <v>149049</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142570</v>
+        <v>142547</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139282</v>
+        <v>139259</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135434</v>
+        <v>135411</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124413</v>
+        <v>124390</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119830</v>
+        <v>119807</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116212</v>
+        <v>116189</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115208</v>
+        <v>115185</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110113</v>
+        <v>110090</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101098</v>
+        <v>101075</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97278</v>
+        <v>97255</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93675</v>
+        <v>93652</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93173</v>
+        <v>93150</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89601</v>
+        <v>89578</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88090</v>
+        <v>88067</v>
       </c>
     </row>
     <row r="6">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>64</v>
@@ -6736,7 +6736,7 @@
         <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>60</v>
@@ -6751,28 +6751,28 @@
         <v>38</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.414</v>
+        <v>0.439</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>154105</v>
+        <v>176993</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>612</v>
+        <v>660</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9366,7 +9366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 10, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 11, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9463,10 +9463,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3444</v>
+        <v>3923</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>50399</v>
+        <v>70032</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1202</v>
+        <v>1491</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32141</v>
+        <v>32722</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>10302</v>
+        <v>13600</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9599,19 +9599,19 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
+          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6589</v>
+        <v>8696</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9632,19 +9632,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>4544</v>
+        <v>6625</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>44</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>70032</v>
+        <v>70280</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32722</v>
+        <v>32731</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>13600</v>
+        <v>13628</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8696</v>
+        <v>8743</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6625</v>
+        <v>6624</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>136</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3922</v>
+        <v>3974</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>44</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>70280</v>
+        <v>70723</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>13628</v>
+        <v>13689</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8743</v>
+        <v>9031</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>98614</v>
+        <v>108859</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>77719</v>
+        <v>130803</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7462</v>
+        <v>12121</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25874</v>
@@ -1014,7 +1014,7 @@
         <v>24712</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>22848</v>
+        <v>23048</v>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>3174</v>
+        <v>6361</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>4136</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>12695</v>
+        <v>25445</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>62039</v>
@@ -5581,67 +5581,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181848</v>
+        <v>181830</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179612</v>
+        <v>179594</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172881</v>
+        <v>172863</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162971</v>
+        <v>162953</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>157017</v>
+        <v>156999</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153534</v>
+        <v>153516</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149049</v>
+        <v>149031</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142547</v>
+        <v>142529</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139259</v>
+        <v>139241</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135411</v>
+        <v>135393</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124390</v>
+        <v>124372</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119807</v>
+        <v>119789</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116189</v>
+        <v>116171</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115185</v>
+        <v>115167</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110090</v>
+        <v>110072</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101075</v>
+        <v>101057</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97255</v>
+        <v>97237</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93652</v>
+        <v>93634</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93150</v>
+        <v>93132</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89578</v>
+        <v>89560</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88067</v>
+        <v>88049</v>
       </c>
     </row>
     <row r="6">
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.439</v>
+        <v>0.544</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>176993</v>
+        <v>240352</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>660</v>
+        <v>690</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3974</v>
+        <v>4022</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>44</v>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>70723</v>
+        <v>72119</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1513</v>
+        <v>1538</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,10 +9542,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32731</v>
+        <v>32804</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9575,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>13689</v>
+        <v>13788</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9031</v>
+        <v>9778</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9641,10 +9641,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6624</v>
+        <v>6632</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>108859</v>
+        <v>108843</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>130803</v>
+        <v>130778</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1487,8 +1487,10 @@
       <c r="J5" s="6" t="n">
         <v>5522</v>
       </c>
-      <c r="K5" s="6" t="n">
-        <v>3</v>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -1586,8 +1588,10 @@
       <c r="J6" s="6" t="n">
         <v>49702</v>
       </c>
-      <c r="K6" s="6" t="n">
-        <v>27</v>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -8935,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>240352</v>
+        <v>240309</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9148,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9366,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 11, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 12, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9463,10 +9467,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4022</v>
+        <v>5127</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9509,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>72119</v>
+        <v>74323</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1538</v>
+        <v>1580</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9542,10 +9546,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32804</v>
+        <v>32986</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9575,10 +9579,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>13788</v>
+        <v>14118</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9608,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9778</v>
+        <v>11774</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9641,7 +9645,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6632</v>
+        <v>6646</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>137</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6728,19 +6728,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>60</v>
@@ -6749,16 +6749,16 @@
         <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>38</v>
@@ -6773,7 +6773,7 @@
         <v>30</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>30</v>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5127</v>
+        <v>5258</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>74323</v>
+        <v>74682</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1580</v>
+        <v>1587</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>32986</v>
+        <v>33025</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>577</v>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14118</v>
+        <v>14206</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>11774</v>
+        <v>12282</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6646</v>
+        <v>6647</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>137</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>108843</v>
+        <v>114631</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>130778</v>
+        <v>177098</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181830</v>
+        <v>181812</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179594</v>
+        <v>179576</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172863</v>
+        <v>172845</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162953</v>
+        <v>162935</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156999</v>
+        <v>156981</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153516</v>
+        <v>153498</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149031</v>
+        <v>149013</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142529</v>
+        <v>142511</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139241</v>
+        <v>139223</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135393</v>
+        <v>135375</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124372</v>
+        <v>124354</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119789</v>
+        <v>119771</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116171</v>
+        <v>116153</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115167</v>
+        <v>115149</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110072</v>
+        <v>110054</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101057</v>
+        <v>101039</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97237</v>
+        <v>97219</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93634</v>
+        <v>93616</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93132</v>
+        <v>93114</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89560</v>
+        <v>89542</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88049</v>
+        <v>88031</v>
       </c>
     </row>
     <row r="6">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.544</v>
+        <v>0.606</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>240309</v>
+        <v>292465</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 12, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 13, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5258</v>
+        <v>5788</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>49</v>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>74682</v>
+        <v>75969</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1587</v>
+        <v>1607</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33025</v>
+        <v>33343</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14206</v>
+        <v>14422</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12282</v>
+        <v>13308</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6647</v>
+        <v>6667</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>137</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>114631</v>
+        <v>120244</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>177098</v>
+        <v>193079</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181812</v>
+        <v>181805</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179576</v>
+        <v>179569</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172845</v>
+        <v>172838</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162935</v>
+        <v>162928</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156981</v>
+        <v>156974</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153498</v>
+        <v>153491</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149013</v>
+        <v>149006</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142511</v>
+        <v>142504</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139223</v>
+        <v>139216</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135375</v>
+        <v>135368</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124354</v>
+        <v>124347</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119771</v>
+        <v>119764</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116153</v>
+        <v>116146</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115149</v>
+        <v>115142</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110054</v>
+        <v>110047</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101039</v>
+        <v>101032</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97219</v>
+        <v>97212</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93616</v>
+        <v>93609</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93114</v>
+        <v>93107</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89542</v>
+        <v>89535</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88031</v>
+        <v>88024</v>
       </c>
     </row>
     <row r="6">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>51</v>
@@ -6743,25 +6743,25 @@
         <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>56</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>55</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>31</v>
@@ -6770,13 +6770,13 @@
         <v>24</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.606</v>
+        <v>0.615</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>292465</v>
+        <v>314099</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>736</v>
+        <v>776</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 13, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 14, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5788</v>
+        <v>5901</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>75969</v>
+        <v>76276</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33343</v>
+        <v>33421</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>584</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14422</v>
+        <v>14468</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13308</v>
+        <v>13528</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5901</v>
+        <v>5973</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>50</v>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>76276</v>
+        <v>76554</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33421</v>
+        <v>33584</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14468</v>
+        <v>14521</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13528</v>
+        <v>13650</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6667</v>
+        <v>6676</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>137</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>120244</v>
+        <v>125837</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>193079</v>
+        <v>206191</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181805</v>
+        <v>181810</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179569</v>
+        <v>179574</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172838</v>
+        <v>172843</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162928</v>
+        <v>162933</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156974</v>
+        <v>156979</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153491</v>
+        <v>153496</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149006</v>
+        <v>149011</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142504</v>
+        <v>142509</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139216</v>
+        <v>139221</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135368</v>
+        <v>135373</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124347</v>
+        <v>124352</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119764</v>
+        <v>119769</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116146</v>
+        <v>116151</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115142</v>
+        <v>115147</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110047</v>
+        <v>110052</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101032</v>
+        <v>101037</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97212</v>
+        <v>97217</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93609</v>
+        <v>93614</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93107</v>
+        <v>93112</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89535</v>
+        <v>89540</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88024</v>
+        <v>88029</v>
       </c>
     </row>
     <row r="6">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.615</v>
+        <v>0.619</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>314099</v>
+        <v>332844</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 14, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 15, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5973</v>
+        <v>6092</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>50</v>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>76554</v>
+        <v>77162</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1619</v>
+        <v>1630</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,10 +9546,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33584</v>
+        <v>33631</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14521</v>
+        <v>14519</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>241</v>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>13650</v>
+        <v>14037</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9636,19 +9636,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Wilt's Career vs. Today's Bag: Channing's BRUTALLY HONEST Take! #nba #basketball</t>
+          <t>Was This The Ultimate Retro Gaming Exploit #nba #basketball #nbajam</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6676</v>
+        <v>7009</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>125837</v>
+        <v>130506</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>206191</v>
+        <v>216653</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181810</v>
+        <v>181809</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179574</v>
+        <v>179573</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172843</v>
+        <v>172842</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162933</v>
+        <v>162932</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156979</v>
+        <v>156978</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153496</v>
+        <v>153495</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149011</v>
+        <v>149010</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142509</v>
+        <v>142508</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139221</v>
+        <v>139220</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135373</v>
+        <v>135372</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124352</v>
+        <v>124351</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119769</v>
+        <v>119768</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116151</v>
+        <v>116150</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115147</v>
+        <v>115146</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110052</v>
+        <v>110051</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101037</v>
+        <v>101036</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97217</v>
+        <v>97216</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93614</v>
+        <v>93613</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93112</v>
+        <v>93111</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89540</v>
+        <v>89539</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88029</v>
+        <v>88028</v>
       </c>
     </row>
     <row r="6">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.619</v>
+        <v>0.623</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>332844</v>
+        <v>348009</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 15, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 16, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9467,7 +9467,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>6092</v>
+        <v>6192</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>50</v>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>77162</v>
+        <v>77783</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1630</v>
+        <v>1644</v>
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>33631</v>
+        <v>33667</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>587</v>
@@ -9570,19 +9570,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
+          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>14519</v>
+        <v>16364</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -9603,19 +9603,19 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>14037</v>
+        <v>14553</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9636,19 +9636,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Was This The Ultimate Retro Gaming Exploit #nba #basketball #nbajam</t>
+          <t>The Real Reason Ja Morant Needed a Change of Scenery! #nba #portlandtrailblazers</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7009</v>
+        <v>8205</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>124</v>
+        <v>251</v>
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -129,7 +129,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -139,6 +138,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>130506</v>
+        <v>135368</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>216653</v>
+        <v>224306</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181809</v>
+        <v>181803</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179573</v>
+        <v>179567</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172842</v>
+        <v>172836</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162932</v>
+        <v>162926</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156978</v>
+        <v>156972</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153495</v>
+        <v>153489</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149010</v>
+        <v>149004</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142508</v>
+        <v>142502</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139220</v>
+        <v>139214</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135372</v>
+        <v>135366</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124351</v>
+        <v>124345</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119768</v>
+        <v>119762</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116150</v>
+        <v>116144</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115146</v>
+        <v>115140</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110051</v>
+        <v>110045</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101036</v>
+        <v>101030</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97216</v>
+        <v>97210</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93613</v>
+        <v>93607</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93111</v>
+        <v>93105</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89539</v>
+        <v>89533</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88028</v>
+        <v>88022</v>
       </c>
     </row>
     <row r="6">
@@ -6728,55 +6728,55 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="K8" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>39</v>
-      </c>
       <c r="N8" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.623</v>
+        <v>0.622</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>348009</v>
+        <v>360557</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9355,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 16, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 17, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9430,10 +9430,36 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="14" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>No data for this period</t>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>The NBA Is BACK! Road Trippin’ Locks In MVP, DPOY &amp; Championship Picks</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>12105</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>237</v>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
         </is>
       </c>
     </row>
@@ -9451,218 +9477,317 @@
       <c r="G7" s="14" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>6192</v>
+        <v>6287</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>NextDerrickRose Clip</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>PAYKATORNAH Clip</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>2KRatings Clip</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>77783</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>1644</v>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="D14" s="7" t="n">
+        <v>77928</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1645</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>33667</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="D15" s="6" t="n">
+        <v>33677</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>587</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>16364</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>320</v>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="D16" s="7" t="n">
+        <v>19305</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>359</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>14553</v>
-      </c>
-      <c r="E14" s="6" t="n">
+      <c r="D17" s="6" t="n">
+        <v>14590</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>244</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>The Real Reason Ja Morant Needed a Change of Scenery! #nba #portlandtrailblazers</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>8205</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>251</v>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="D18" s="7" t="n">
+        <v>8719</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>270</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9670,7 +9795,7 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>135368</v>
+        <v>139987</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>224306</v>
+        <v>232779</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>883</v>
+        <v>982</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181803</v>
+        <v>181801</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179567</v>
+        <v>179565</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172836</v>
+        <v>172834</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162926</v>
+        <v>162924</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156972</v>
+        <v>156970</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153489</v>
+        <v>153487</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149004</v>
+        <v>149002</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142502</v>
+        <v>142500</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139214</v>
+        <v>139212</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135366</v>
+        <v>135364</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124345</v>
+        <v>124343</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119762</v>
+        <v>119760</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116144</v>
+        <v>116142</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115140</v>
+        <v>115138</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110045</v>
+        <v>110043</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101030</v>
+        <v>101028</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97210</v>
+        <v>97208</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93607</v>
+        <v>93605</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93105</v>
+        <v>93103</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89533</v>
+        <v>89531</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88022</v>
+        <v>88020</v>
       </c>
     </row>
     <row r="6">
@@ -6728,31 +6728,31 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>36</v>
@@ -6776,7 +6776,7 @@
         <v>38</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.622</v>
+        <v>0.623</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>360557</v>
+        <v>373748</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>883</v>
+        <v>982</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 17, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 18, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>12105</v>
+        <v>42881</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>237</v>
+        <v>619</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9484,19 +9484,19 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
+          <t>Perk Had a LOT to Say About His Viral 2K Rating</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>6287</v>
+        <v>6781</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9517,19 +9517,19 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>NextDerrickRose Clip</t>
+          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>6353</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9550,19 +9550,19 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>PAYKATORNAH Clip</t>
+          <t>Perk Makes BOLD Proclamation About Caleb Wilson—Channing Isn’t Buying It</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>3273</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>2KRatings Clip</t>
+          <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>77928</v>
+        <v>78030</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33677</v>
+        <v>33706</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>587</v>
@@ -9695,19 +9695,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>19305</v>
+        <v>20965</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>359</v>
+        <v>463</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9728,19 +9728,19 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
+          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14590</v>
+        <v>20254</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>244</v>
+        <v>368</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9761,19 +9761,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>The Real Reason Ja Morant Needed a Change of Scenery! #nba #portlandtrailblazers</t>
+          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>8719</v>
+        <v>14648</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>42881</v>
+        <v>46427</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>619</v>
+        <v>669</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>6781</v>
+        <v>7714</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6353</v>
+        <v>6362</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>51</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>3273</v>
+        <v>4112</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9588,14 +9588,14 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78030</v>
+        <v>78040</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33706</v>
+        <v>33709</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>587</v>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>20965</v>
+        <v>24979</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20254</v>
+        <v>20327</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>368</v>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14648</v>
+        <v>14656</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>246</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46427</v>
+        <v>47792</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>7714</v>
+        <v>8334</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6362</v>
+        <v>6361</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>51</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>4112</v>
+        <v>4453</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>59</v>
+        <v>287</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78040</v>
+        <v>78058</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1647</v>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>24979</v>
+        <v>25564</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20327</v>
+        <v>20328</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>368</v>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14656</v>
+        <v>14660</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>246</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>139987</v>
+        <v>154449</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>232779</v>
+        <v>246012</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>982</v>
+        <v>1068</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181801</v>
+        <v>181784</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179565</v>
+        <v>179548</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172834</v>
+        <v>172817</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162924</v>
+        <v>162907</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156970</v>
+        <v>156953</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153487</v>
+        <v>153470</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149002</v>
+        <v>148985</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142500</v>
+        <v>142483</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139212</v>
+        <v>139195</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135364</v>
+        <v>135347</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124343</v>
+        <v>124326</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119760</v>
+        <v>119743</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116142</v>
+        <v>116125</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115138</v>
+        <v>115121</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110043</v>
+        <v>110026</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101028</v>
+        <v>101011</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97208</v>
+        <v>97191</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93605</v>
+        <v>93588</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93103</v>
+        <v>93086</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89531</v>
+        <v>89514</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88020</v>
+        <v>88003</v>
       </c>
     </row>
     <row r="6">
@@ -6728,43 +6728,43 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>34</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>25</v>
@@ -6773,10 +6773,10 @@
         <v>26</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.623</v>
+        <v>0.613</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>373748</v>
+        <v>401529</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>982</v>
+        <v>1068</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 18, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 19, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>47792</v>
+        <v>68680</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>681</v>
+        <v>873</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>8334</v>
+        <v>18920</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6361</v>
+        <v>6405</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>4453</v>
+        <v>6216</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>287</v>
+        <v>2602</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78058</v>
+        <v>78167</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1647</v>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33709</v>
+        <v>33739</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>587</v>
@@ -9704,10 +9704,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>25564</v>
+        <v>27881</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>514</v>
+        <v>548</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20328</v>
+        <v>20788</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9761,19 +9761,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Are the Wizards PLAYOFF BOUND?! #nba #basketball</t>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14660</v>
+        <v>19124</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>246</v>
+        <v>680</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>68680</v>
+        <v>68757</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>18920</v>
+        <v>19030</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>146</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6216</v>
+        <v>6220</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2602</v>
+        <v>2614</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>20</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>27881</v>
+        <v>27889</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>548</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20788</v>
+        <v>20818</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>19124</v>
+        <v>19296</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>68757</v>
+        <v>69328</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>19030</v>
+        <v>19432</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6405</v>
+        <v>6412</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>53</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6220</v>
+        <v>6274</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>64</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2614</v>
+        <v>2651</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>20</v>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33739</v>
+        <v>33749</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>587</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>27889</v>
+        <v>27926</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>548</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20818</v>
+        <v>20830</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>19296</v>
+        <v>20218</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>685</v>
+        <v>719</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>154449</v>
+        <v>199452</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>246012</v>
+        <v>272505</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1068</v>
+        <v>1149</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181784</v>
+        <v>181698</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179548</v>
+        <v>179462</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172817</v>
+        <v>172731</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162907</v>
+        <v>162821</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156953</v>
+        <v>156867</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153470</v>
+        <v>153384</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148985</v>
+        <v>148899</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142483</v>
+        <v>142397</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139195</v>
+        <v>139109</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135347</v>
+        <v>135261</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124326</v>
+        <v>124240</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119743</v>
+        <v>119657</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116125</v>
+        <v>116039</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115121</v>
+        <v>115035</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110026</v>
+        <v>109940</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101011</v>
+        <v>100925</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97191</v>
+        <v>97105</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93588</v>
+        <v>93502</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93086</v>
+        <v>93000</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89514</v>
+        <v>89428</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88003</v>
+        <v>87917</v>
       </c>
     </row>
     <row r="6">
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>64</v>
@@ -6740,10 +6740,10 @@
         <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>54</v>
@@ -6752,10 +6752,10 @@
         <v>60</v>
       </c>
       <c r="J8" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="K8" s="7" t="n">
         <v>34</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>35</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>25</v>
@@ -6764,19 +6764,19 @@
         <v>39</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.613</v>
+        <v>0.576</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>401529</v>
+        <v>473106</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1068</v>
+        <v>1149</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 19, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 20, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>69328</v>
+        <v>80807</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>885</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>19432</v>
+        <v>25979</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9517,19 +9517,19 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
+          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6412</v>
+        <v>9356</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9550,19 +9550,19 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Perk Makes BOLD Proclamation About Caleb Wilson—Channing Isn’t Buying It</t>
+          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6274</v>
+        <v>6471</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2651</v>
+        <v>3815</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78167</v>
+        <v>78307</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9662,19 +9662,19 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>33749</v>
+        <v>35287</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>587</v>
+        <v>1019</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9695,19 +9695,19 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>27926</v>
+        <v>33777</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>548</v>
+        <v>588</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9728,19 +9728,19 @@
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20830</v>
+        <v>29294</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>375</v>
+        <v>568</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9761,19 +9761,19 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
+          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>20218</v>
+        <v>21276</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>719</v>
+        <v>381</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>80807</v>
+        <v>82884</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1000</v>
+        <v>1023</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>25979</v>
+        <v>26750</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>9356</v>
+        <v>10076</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6471</v>
+        <v>6485</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>53</v>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3815</v>
+        <v>4182</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78307</v>
+        <v>78330</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1649</v>
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>35287</v>
+        <v>36446</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1019</v>
+        <v>1040</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>33777</v>
+        <v>33783</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>588</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>29294</v>
+        <v>29545</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>21276</v>
+        <v>21309</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>82884</v>
+        <v>82987</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1023</v>
+        <v>1028</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>26750</v>
+        <v>26796</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>192</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10076</v>
+        <v>10104</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>95</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4182</v>
+        <v>4193</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>33</v>
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>36446</v>
+        <v>36467</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>199452</v>
+        <v>245329</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>272505</v>
+        <v>307575</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1149</v>
+        <v>1283</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181698</v>
+        <v>181559</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179462</v>
+        <v>179323</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172731</v>
+        <v>172592</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162821</v>
+        <v>162682</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156867</v>
+        <v>156728</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153384</v>
+        <v>153245</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148899</v>
+        <v>148760</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142397</v>
+        <v>142258</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139109</v>
+        <v>138970</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135261</v>
+        <v>135122</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124240</v>
+        <v>124101</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119657</v>
+        <v>119518</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116039</v>
+        <v>115900</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115035</v>
+        <v>114896</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109940</v>
+        <v>109801</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100925</v>
+        <v>100786</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97105</v>
+        <v>96966</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93502</v>
+        <v>93363</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93000</v>
+        <v>92861</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89428</v>
+        <v>89289</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87917</v>
+        <v>87778</v>
       </c>
     </row>
     <row r="6">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.576</v>
+        <v>0.555</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>473106</v>
+        <v>554187</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1149</v>
+        <v>1283</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>82987</v>
+        <v>83265</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1028</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>26796</v>
+        <v>26883</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>192</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10104</v>
+        <v>10166</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>95</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6485</v>
+        <v>6487</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>53</v>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>78330</v>
+        <v>78329</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>1649</v>
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>36467</v>
+        <v>36552</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>21309</v>
+        <v>21348</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>382</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>245329</v>
+        <v>245094</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>307575</v>
+        <v>307444</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1283</v>
+        <v>1238</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -6728,55 +6728,55 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>64</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>554187</v>
+        <v>553776</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1283</v>
+        <v>1238</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9355,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 20, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 21, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>83265</v>
+        <v>85506</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1028</v>
+        <v>1037</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9463,251 +9463,251 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>13498</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>226</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="14" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Perk Had a LOT to Say About His Viral 2K Rating</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>26883</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>192</v>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="D9" s="7" t="n">
+        <v>29268</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>216</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>10166</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="D10" s="6" t="n">
+        <v>12233</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>6487</v>
-      </c>
-      <c r="E10" s="7" t="n">
+      <c r="D11" s="7" t="n">
+        <v>6508</v>
+      </c>
+      <c r="E11" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>4193</v>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="D12" s="6" t="n">
+        <v>4963</v>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NewLook76ers Clip</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>78329</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>1649</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>36552</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1042</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>#3</t>
+          <t>#1</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>33783</v>
+        <v>78348</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>588</v>
+        <v>1649</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9723,24 +9723,24 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>#4</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
-          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>29545</v>
+        <v>39279</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>570</v>
+        <v>1183</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9756,38 +9756,104 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>33798</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>588</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>30317</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>585</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>21348</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>382</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="D20" s="7" t="n">
+        <v>21590</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>385</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9795,9 +9861,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A8:G8"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>245094</v>
+        <v>281836</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>307444</v>
+        <v>366098</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1238</v>
+        <v>1393</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181559</v>
+        <v>181437</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179323</v>
+        <v>179201</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172592</v>
+        <v>172470</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162682</v>
+        <v>162560</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156728</v>
+        <v>156606</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153245</v>
+        <v>153123</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148760</v>
+        <v>148638</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142258</v>
+        <v>142136</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138970</v>
+        <v>138848</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135122</v>
+        <v>135000</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124101</v>
+        <v>123979</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119518</v>
+        <v>119396</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115900</v>
+        <v>115778</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114896</v>
+        <v>114774</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109801</v>
+        <v>109679</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100786</v>
+        <v>100664</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96966</v>
+        <v>96844</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93363</v>
+        <v>93241</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92861</v>
+        <v>92739</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89289</v>
+        <v>89167</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87778</v>
+        <v>87656</v>
       </c>
     </row>
     <row r="6">
@@ -6728,40 +6728,40 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E8" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="I8" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>62</v>
-      </c>
       <c r="J8" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N8" s="7" t="n">
         <v>30</v>
@@ -6770,13 +6770,13 @@
         <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.555</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>553776</v>
+        <v>649327</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1238</v>
+        <v>1393</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 21, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 22, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>85506</v>
+        <v>86494</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13498</v>
+        <v>26344</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>226</v>
+        <v>458</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>29268</v>
+        <v>33736</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9550,19 +9550,19 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
+          <t>Can LeBron, Embiid &amp; Jaylen Brown Actually Make This Work?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>12233</v>
+        <v>22194</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9583,19 +9583,19 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
+          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>6508</v>
+        <v>13645</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9616,19 +9616,19 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
+          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4963</v>
+        <v>6512</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9649,19 +9649,19 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NewLook76ers Clip</t>
+          <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>5504</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>78348</v>
+        <v>78366</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>1649</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>39279</v>
+        <v>42737</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1183</v>
+        <v>1337</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>33798</v>
+        <v>33816</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>588</v>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>30317</v>
+        <v>31242</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9827,19 +9827,19 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>The Truth About Giannis in Miami... #nba #basketball #miamiheat</t>
+          <t>ESPN’s Kendrick Perkins CALLS OUT The Ultimate Championship Lie! #NBA #Celtics</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>21590</v>
+        <v>23485</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>385</v>
+        <v>461</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>86494</v>
+        <v>86548</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1048</v>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26344</v>
+        <v>26791</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>33736</v>
+        <v>33993</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22194</v>
+        <v>23371</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>13645</v>
+        <v>13675</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>128</v>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5504</v>
+        <v>5540</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>37</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>42737</v>
+        <v>42799</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>23485</v>
+        <v>23563</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -6728,55 +6728,55 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>51</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>32</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>41</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>86548</v>
+        <v>86596</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1048</v>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>26791</v>
+        <v>28112</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>33993</v>
+        <v>34630</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>23371</v>
+        <v>26187</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>13675</v>
+        <v>13688</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>128</v>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5540</v>
+        <v>5557</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>37</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>78366</v>
+        <v>78369</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>1649</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>42799</v>
+        <v>42973</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>31242</v>
+        <v>31320</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>593</v>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>23563</v>
+        <v>23621</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>281836</v>
+        <v>311942</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>366098</v>
+        <v>397445</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1393</v>
+        <v>1462</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181437</v>
+        <v>181303</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179201</v>
+        <v>179067</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172470</v>
+        <v>172336</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162560</v>
+        <v>162426</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156606</v>
+        <v>156472</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153123</v>
+        <v>152989</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148638</v>
+        <v>148504</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142136</v>
+        <v>142002</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138848</v>
+        <v>138714</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135000</v>
+        <v>134866</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123979</v>
+        <v>123845</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119396</v>
+        <v>119262</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115778</v>
+        <v>115644</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114774</v>
+        <v>114640</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109679</v>
+        <v>109545</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100664</v>
+        <v>100530</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96844</v>
+        <v>96710</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93241</v>
+        <v>93107</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92739</v>
+        <v>92605</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89167</v>
+        <v>89033</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87656</v>
+        <v>87522</v>
       </c>
     </row>
     <row r="6">
@@ -6728,58 +6728,58 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>51</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>41</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T8" s="7" t="n">
         <v>11</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>649327</v>
+        <v>710849</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1393</v>
+        <v>1462</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9355,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 22, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 23, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>86596</v>
+        <v>86943</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>28112</v>
+        <v>31915</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9496,364 +9496,397 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>NBA Opening Night: Ant &amp; LaMelo Drop 66, Portland ROLLS &amp; Haliburton Returns</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>26125</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>357</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="n"/>
+      <c r="G9" s="14" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Perk Had a LOT to Say About His Viral 2K Rating</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>34630</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>241</v>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="D10" s="7" t="n">
+        <v>39366</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>273</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Can LeBron, Embiid &amp; Jaylen Brown Actually Make This Work?</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>26187</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>212</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="D11" s="6" t="n">
+        <v>32559</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>251</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>13688</v>
-      </c>
-      <c r="E11" s="7" t="n">
+      <c r="D12" s="7" t="n">
+        <v>13770</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>128</v>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>6512</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="D13" s="6" t="n">
+        <v>6516</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>5557</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="D14" s="7" t="n">
+        <v>5583</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>★ TOP SHORTS</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>78369</v>
-      </c>
-      <c r="E16" s="7" t="n">
+      <c r="D17" s="7" t="n">
+        <v>78382</v>
+      </c>
+      <c r="E17" s="7" t="n">
         <v>1649</v>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>42973</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>1344</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="D18" s="6" t="n">
+        <v>43610</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1364</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>33816</v>
-      </c>
-      <c r="E18" s="7" t="n">
+      <c r="D19" s="7" t="n">
+        <v>33826</v>
+      </c>
+      <c r="E19" s="7" t="n">
         <v>588</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>31320</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D20" s="6" t="n">
+        <v>31592</v>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>593</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins CALLS OUT The Ultimate Championship Lie! #NBA #Celtics</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>23621</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>463</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>30256</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>902</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9861,8 +9894,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A9:G9"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>311942</v>
+        <v>359277</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>397445</v>
+        <v>449451</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1462</v>
+        <v>1513</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181303</v>
+        <v>181172</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179067</v>
+        <v>178936</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172336</v>
+        <v>172205</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162426</v>
+        <v>162295</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156472</v>
+        <v>156341</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152989</v>
+        <v>152858</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148504</v>
+        <v>148373</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142002</v>
+        <v>141871</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138714</v>
+        <v>138583</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134866</v>
+        <v>134735</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123845</v>
+        <v>123714</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119262</v>
+        <v>119131</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115644</v>
+        <v>115513</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114640</v>
+        <v>114509</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109545</v>
+        <v>109414</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100530</v>
+        <v>100399</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96710</v>
+        <v>96579</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93107</v>
+        <v>92976</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92605</v>
+        <v>92474</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89033</v>
+        <v>88902</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87522</v>
+        <v>87391</v>
       </c>
     </row>
     <row r="6">
@@ -6728,52 +6728,52 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>57</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>54</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>41</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>27</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>31</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>710849</v>
+        <v>810241</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1462</v>
+        <v>1513</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 23, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 24, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>86943</v>
+        <v>87277</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9471,19 +9471,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
+          <t>NBA Opening Night: Ant &amp; LaMelo Drop 66, Portland ROLLS &amp; Haliburton Returns</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>31915</v>
+        <v>39006</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9504,19 +9504,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>NBA Opening Night: Ant &amp; LaMelo Drop 66, Portland ROLLS &amp; Haliburton Returns</t>
+          <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>26125</v>
+        <v>32875</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>357</v>
+        <v>533</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>39366</v>
+        <v>43070</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>32559</v>
+        <v>35796</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>13770</v>
+        <v>13796</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>128</v>
@@ -9649,19 +9649,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
+          <t>Perk Says Yaxel Didn’t Back Down From Luka — And Luka Made Him Pay</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6516</v>
+        <v>13229</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9682,19 +9682,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Perk Says the Knicks Can’t Ask KAT to Take Jalen Duren Money</t>
+          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5583</v>
+        <v>6517</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9728,19 +9728,19 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
+          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>78382</v>
+        <v>86125</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1649</v>
+        <v>2189</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9761,19 +9761,19 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>43610</v>
+        <v>78388</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1364</v>
+        <v>1649</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9794,19 +9794,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>33826</v>
+        <v>44561</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>588</v>
+        <v>1392</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9827,19 +9827,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>31592</v>
+        <v>33840</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9860,19 +9860,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
+          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>30256</v>
+        <v>32039</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>902</v>
+        <v>596</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>359277</v>
+        <v>418632</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>449451</v>
+        <v>499152</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1513</v>
+        <v>1572</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>182000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181172</v>
+        <v>181025</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178936</v>
+        <v>178789</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172205</v>
+        <v>172058</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162295</v>
+        <v>162148</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156341</v>
+        <v>156194</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152858</v>
+        <v>152711</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148373</v>
+        <v>148226</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141871</v>
+        <v>141724</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138583</v>
+        <v>138436</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134735</v>
+        <v>134588</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123714</v>
+        <v>123567</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119131</v>
+        <v>118984</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115513</v>
+        <v>115366</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114509</v>
+        <v>114362</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109414</v>
+        <v>109267</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100399</v>
+        <v>100252</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96579</v>
+        <v>96432</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92976</v>
+        <v>92829</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92474</v>
+        <v>92327</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88902</v>
+        <v>88755</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87391</v>
+        <v>87244</v>
       </c>
     </row>
     <row r="6">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.555</v>
+        <v>0.543</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>810241</v>
+        <v>919356</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1513</v>
+        <v>1572</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 24, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 25, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>87277</v>
+        <v>87590</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>39006</v>
+        <v>44281</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>531</v>
+        <v>591</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>32875</v>
+        <v>33548</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>43070</v>
+        <v>48311</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>35796</v>
+        <v>40588</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9616,19 +9616,19 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
+          <t>Yaxel Talking Trash to Luka is Why We LOVE The NBA</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>13796</v>
+        <v>19641</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9649,19 +9649,19 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Perk Says Yaxel Didn’t Back Down From Luka — And Luka Made Him Pay</t>
+          <t>Was LaMelo Ball’s Move a Travel? Richard Jefferson Explains the Rule</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>13229</v>
+        <v>16439</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9682,19 +9682,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Kevin Love Was BARBECUE CHICKEN, Giannis in Miami &amp; Clippers Are SCREWED</t>
+          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>6517</v>
+        <v>13870</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>86125</v>
+        <v>112586</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2189</v>
+        <v>2751</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78388</v>
+        <v>78408</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>44561</v>
+        <v>45384</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1392</v>
+        <v>1406</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33840</v>
+        <v>33849</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>588</v>
@@ -9869,10 +9869,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32039</v>
+        <v>32389</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>418632</v>
+        <v>471683</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>499152</v>
+        <v>589294</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1572</v>
+        <v>1615</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5582,70 +5582,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>182000</v>
+        <v>183000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181025</v>
+        <v>181915</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>178789</v>
+        <v>179679</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172058</v>
+        <v>172948</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162148</v>
+        <v>163038</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156194</v>
+        <v>157084</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>152711</v>
+        <v>153601</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148226</v>
+        <v>149116</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>141724</v>
+        <v>142614</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138436</v>
+        <v>139326</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>134588</v>
+        <v>135478</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>123567</v>
+        <v>124457</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>118984</v>
+        <v>119874</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115366</v>
+        <v>116256</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114362</v>
+        <v>115252</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109267</v>
+        <v>110157</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100252</v>
+        <v>101142</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96432</v>
+        <v>97322</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>92829</v>
+        <v>93719</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92327</v>
+        <v>93217</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>88755</v>
+        <v>89645</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87244</v>
+        <v>88134</v>
       </c>
     </row>
     <row r="6">
@@ -6728,16 +6728,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>57</v>
@@ -6749,22 +6749,22 @@
         <v>53</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
         <v>23</v>
@@ -6773,13 +6773,13 @@
         <v>27</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" s="7" t="n">
         <v>11</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.543</v>
+        <v>0.555</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>919356</v>
+        <v>1062592</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1572</v>
+        <v>1615</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 25, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 26, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>87590</v>
+        <v>88013</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>44281</v>
+        <v>47757</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>591</v>
+        <v>625</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>33548</v>
+        <v>34272</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>48311</v>
+        <v>50809</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>40588</v>
+        <v>48351</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>19641</v>
+        <v>30953</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>16439</v>
+        <v>23110</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>13870</v>
+        <v>13989</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>112586</v>
+        <v>126499</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2751</v>
+        <v>3077</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78408</v>
+        <v>78433</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>45384</v>
+        <v>46077</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1406</v>
+        <v>1426</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33849</v>
+        <v>33861</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>588</v>
@@ -9869,10 +9869,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32389</v>
+        <v>32777</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88013</v>
+        <v>88033</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>47757</v>
+        <v>47866</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34272</v>
+        <v>34314</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>549</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>50809</v>
+        <v>51019</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>48351</v>
+        <v>48324</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>329</v>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>30953</v>
+        <v>31359</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>23110</v>
+        <v>23347</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>13989</v>
+        <v>13999</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>129</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>126499</v>
+        <v>127072</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3077</v>
+        <v>3086</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78433</v>
+        <v>78435</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1651</v>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32777</v>
+        <v>32772</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>601</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>471683</v>
+        <v>521701</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>589294</v>
+        <v>636243</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1615</v>
+        <v>1669</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>183000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181915</v>
+        <v>181863</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179679</v>
+        <v>179627</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172948</v>
+        <v>172896</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>163038</v>
+        <v>162986</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>157084</v>
+        <v>157032</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153601</v>
+        <v>153549</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149116</v>
+        <v>149064</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142614</v>
+        <v>142562</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139326</v>
+        <v>139274</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135478</v>
+        <v>135426</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124457</v>
+        <v>124405</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119874</v>
+        <v>119822</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116256</v>
+        <v>116204</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115252</v>
+        <v>115200</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110157</v>
+        <v>110105</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101142</v>
+        <v>101090</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97322</v>
+        <v>97270</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93719</v>
+        <v>93667</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93217</v>
+        <v>93165</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89645</v>
+        <v>89593</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88134</v>
+        <v>88082</v>
       </c>
     </row>
     <row r="6">
@@ -6728,25 +6728,25 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>66</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>55</v>
@@ -6755,10 +6755,10 @@
         <v>34</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>40</v>
@@ -6767,16 +6767,16 @@
         <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.555</v>
+        <v>0.549</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1062592</v>
+        <v>1159613</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1615</v>
+        <v>1669</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 26, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 27, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88033</v>
+        <v>88133</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>47866</v>
+        <v>48792</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34314</v>
+        <v>34433</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>51019</v>
+        <v>53476</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>48324</v>
+        <v>48434</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>329</v>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>31359</v>
+        <v>35627</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>23347</v>
+        <v>25070</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9682,19 +9682,19 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>“Chicago Found Its Next Derrick Rose”: Perk Goes All In on Caleb Wilson’s Bulls</t>
+          <t>Portland’s Opening-Night Blowout Has Road Trippin’ Asking Questions</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>13999</v>
+        <v>14618</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>127072</v>
+        <v>131651</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3086</v>
+        <v>3162</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78435</v>
+        <v>78440</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>46077</v>
+        <v>46840</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1426</v>
+        <v>1449</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33861</v>
+        <v>33862</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>588</v>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32772</v>
+        <v>32891</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>601</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88133</v>
+        <v>88134</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1066</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48792</v>
+        <v>48813</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>634</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>53476</v>
+        <v>53599</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>362</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>48434</v>
+        <v>48440</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>329</v>
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>35627</v>
+        <v>35716</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>276</v>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>25070</v>
+        <v>25107</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>181</v>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>131651</v>
+        <v>131776</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3162</v>
+        <v>3164</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78440</v>
+        <v>78442</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1653</v>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>46840</v>
+        <v>46875</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32891</v>
+        <v>32894</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>601</v>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>521701</v>
+        <v>521246</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>636243</v>
+        <v>636002</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -6728,25 +6728,25 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>55</v>
@@ -6758,7 +6758,7 @@
         <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>40</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1159613</v>
+        <v>1158917</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88134</v>
+        <v>88196</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48813</v>
+        <v>49097</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34433</v>
+        <v>34520</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>551</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>53599</v>
+        <v>54706</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>48440</v>
+        <v>48533</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>329</v>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>35716</v>
+        <v>39125</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>25107</v>
+        <v>25391</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>14618</v>
+        <v>15094</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -9737,10 +9737,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>131776</v>
+        <v>134589</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>3164</v>
+        <v>3220</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>1653</v>
@@ -9794,19 +9794,19 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
+          <t>The WORST NBA2k Rating Ever!? #nba #nba2k #retrogaming #nbalive</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>46875</v>
+        <v>71911</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1450</v>
+        <v>2440</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9827,19 +9827,19 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>33862</v>
+        <v>47150</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>588</v>
+        <v>1452</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9860,19 +9860,19 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Did Kendrick Perk just name Chicago Bulls’ ROOKIE next Derrick Rose?! #nba #basketball</t>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>32894</v>
+        <v>33868</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>521246</v>
+        <v>558299</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>636002</v>
+        <v>662700</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1669</v>
+        <v>1711</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -5585,67 +5585,67 @@
         <v>183000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181863</v>
+        <v>181809</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179627</v>
+        <v>179573</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172896</v>
+        <v>172842</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162986</v>
+        <v>162932</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>157032</v>
+        <v>156978</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153549</v>
+        <v>153495</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149064</v>
+        <v>149010</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142562</v>
+        <v>142508</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139274</v>
+        <v>139220</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135426</v>
+        <v>135372</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124405</v>
+        <v>124351</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119822</v>
+        <v>119768</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116204</v>
+        <v>116150</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115200</v>
+        <v>115146</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110105</v>
+        <v>110051</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101090</v>
+        <v>101036</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97270</v>
+        <v>97216</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93667</v>
+        <v>93613</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93165</v>
+        <v>93111</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89593</v>
+        <v>89539</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88082</v>
+        <v>88028</v>
       </c>
     </row>
     <row r="6">
@@ -6728,10 +6728,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>65</v>
@@ -6740,10 +6740,10 @@
         <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>55</v>
@@ -6752,28 +6752,28 @@
         <v>55</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K8" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="M8" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L8" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>40</v>
-      </c>
       <c r="N8" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>31</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.549</v>
+        <v>0.542</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1158917</v>
+        <v>1222710</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1669</v>
+        <v>1711</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9355,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 27, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 28, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88196</v>
+        <v>88359</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>49097</v>
+        <v>49847</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34520</v>
+        <v>34663</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9529,364 +9529,397 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Perk: Tatum &amp; Jaylen Brown NEVER Had a Real Relationship + Fred VanVleet Joins Road Trippin’</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>25698</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>376</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Perk Had a LOT to Say About His Viral 2K Rating</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>54706</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>366</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="D11" s="7" t="n">
+        <v>56859</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>385</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Yaxel Talking Trash to Luka is Why We LOVE The NBA</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>49379</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Can LeBron, Embiid &amp; Jaylen Brown Actually Make This Work?</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>48533</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>329</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="D13" s="7" t="n">
+        <v>48701</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>330</v>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Was LaMelo Ball’s Move a Travel? Richard Jefferson Explains the Rule</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>26808</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Portland’s Opening-Night Blowout Has Road Trippin’ Asking Questions</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>16014</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>The WORST NBA2k Rating Ever!? #nba #nba2k #retrogaming #nbalive</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>480304</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>16229</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>139400</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Yaxel Talking Trash to Luka is Why We LOVE The NBA</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>39125</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>315</v>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>78469</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1655</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Was LaMelo Ball’s Move a Travel? Richard Jefferson Explains the Rule</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>25391</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>186</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>47958</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1474</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Portland’s Opening-Night Blowout Has Road Trippin’ Asking Questions</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>15094</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>33891</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>588</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>134589</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>3220</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>78444</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>1653</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>The WORST NBA2k Rating Ever!? #nba #nba2k #retrogaming #nbalive</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>71911</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>2440</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>47150</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>1452</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n">
-        <v>33868</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>588</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9894,9 +9927,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>558299</v>
+        <v>583564</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>662700</v>
+        <v>752576</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1711</v>
+        <v>1743</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5585,67 +5585,67 @@
         <v>183000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181809</v>
+        <v>181761</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179573</v>
+        <v>179525</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172842</v>
+        <v>172794</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162932</v>
+        <v>162884</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156978</v>
+        <v>156930</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153495</v>
+        <v>153447</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>149010</v>
+        <v>148962</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142508</v>
+        <v>142460</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139220</v>
+        <v>139172</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135372</v>
+        <v>135324</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124351</v>
+        <v>124303</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119768</v>
+        <v>119720</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116150</v>
+        <v>116102</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115146</v>
+        <v>115098</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110051</v>
+        <v>110003</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>101036</v>
+        <v>100988</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97216</v>
+        <v>97168</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93613</v>
+        <v>93565</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93111</v>
+        <v>93063</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89539</v>
+        <v>89491</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>88028</v>
+        <v>87980</v>
       </c>
     </row>
     <row r="6">
@@ -6728,34 +6728,34 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>56</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L8" s="7" t="n">
         <v>26</v>
@@ -6764,16 +6764,16 @@
         <v>37</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>31</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.542</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1222710</v>
+        <v>1337883</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1711</v>
+        <v>1743</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 28, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 29, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88359</v>
+        <v>88467</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1069</v>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>49847</v>
+        <v>50062</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9504,19 +9504,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
+          <t>Perk: Tatum &amp; Jaylen Brown NEVER Had a Real Relationship + Fred VanVleet Joins Road Trippin’</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>34663</v>
+        <v>37909</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9537,19 +9537,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>Perk: Tatum &amp; Jaylen Brown NEVER Had a Real Relationship + Fred VanVleet Joins Road Trippin’</t>
+          <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>25698</v>
+        <v>34749</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>376</v>
+        <v>552</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>56859</v>
+        <v>58860</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>49379</v>
+        <v>55914</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>393</v>
+        <v>444</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>48701</v>
+        <v>48718</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>26808</v>
+        <v>27350</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>16014</v>
+        <v>16547</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -9770,10 +9770,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>480304</v>
+        <v>947391</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>16229</v>
+        <v>31338</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>139400</v>
+        <v>141036</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>3277</v>
+        <v>3295</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>78469</v>
+        <v>78505</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -9869,10 +9869,10 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>47958</v>
+        <v>49212</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1474</v>
+        <v>1503</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -9893,19 +9893,19 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Why Bron is the Ultimate Test in the NBA #nba #basketball #lebronjames</t>
+          <t>ESPN’s Richard Jefferson: Why the Lakers OFFICIALLY Belong to Luka Now #nba</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>33891</v>
+        <v>34320</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>588</v>
+        <v>349</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>583564</v>
+        <v>622195</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>752576</v>
+        <v>1159952</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1743</v>
+        <v>1786</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>4</v>
@@ -5585,67 +5585,67 @@
         <v>183000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181761</v>
+        <v>181564</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179525</v>
+        <v>179328</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172794</v>
+        <v>172597</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162884</v>
+        <v>162687</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156930</v>
+        <v>156733</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153447</v>
+        <v>153250</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148962</v>
+        <v>148765</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142460</v>
+        <v>142263</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>139172</v>
+        <v>138975</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135324</v>
+        <v>135127</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124303</v>
+        <v>124106</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119720</v>
+        <v>119523</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>116102</v>
+        <v>115905</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>115098</v>
+        <v>114901</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>110003</v>
+        <v>109806</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100988</v>
+        <v>100791</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>97168</v>
+        <v>96971</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93565</v>
+        <v>93368</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>93063</v>
+        <v>92866</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89491</v>
+        <v>89294</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87980</v>
+        <v>87783</v>
       </c>
     </row>
     <row r="6">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>35</v>
@@ -6740,40 +6740,40 @@
         <v>51</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>29</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>31</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1337883</v>
+        <v>1783933</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1743</v>
+        <v>1786</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9355,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 29, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 30, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88467</v>
+        <v>88552</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1069</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>50062</v>
+        <v>50197</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>641</v>
@@ -9513,10 +9513,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>37909</v>
+        <v>40831</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>533</v>
+        <v>566</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9537,389 +9537,422 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
+          <t>LeBron Is Coasting While Philly Keeps Winning + Can Steph Hold On Until Jimmy Returns?</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>38891</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>591</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
           <t>NBA Opening Night: Tatum Under PRESSURE, LeBron's Philly Debut &amp; Wemby vs. OKC</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>34749</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>552</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="D9" s="7" t="n">
+        <v>34831</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>553</v>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>LONG</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>★ TOP SEGMENT CLIPS</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Yaxel Talking Trash to Luka is Why We LOVE The NBA</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>63465</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Perk Had a LOT to Say About His Viral 2K Rating</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>58860</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>398</v>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>60997</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Can LeBron, Embiid &amp; Jaylen Brown Actually Make This Work?</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>48726</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>331</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>Was LaMelo Ball’s Move a Travel? Richard Jefferson Explains the Rule</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>27717</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Fred VanVleet Brings the Rockets’ Locker Room to Road Trippin’</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>18216</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>240</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>★ TOP SHORTS</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>The WORST NBA2k Rating Ever!? #nba #nba2k #retrogaming #nbalive</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1303576</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>41444</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>GROUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Yaxel Talking Trash to Luka is Why We LOVE The NBA</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>55914</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>444</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>142152</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>3305</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Can LeBron, Embiid &amp; Jaylen Brown Actually Make This Work?</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>48718</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>331</v>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>78530</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1657</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Was LaMelo Ball’s Move a Travel? Richard Jefferson Explains the Rule</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>27350</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>50024</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1519</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Portland’s Opening-Night Blowout Has Road Trippin’ Asking Questions</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>16547</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>102</v>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>ESPN’s Richard Jefferson: Why the Lakers OFFICIALLY Belong to Luka Now #nba</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>34521</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>★ TOP SHORTS</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>The WORST NBA2k Rating Ever!? #nba #nba2k #retrogaming #nbalive</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>947391</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>31338</v>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>ESPN’s Richard Jefferson Explains Why Luka Doncic DESTROYED The Warriors’ Rookie #nba #Lakers</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>141036</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>3295</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Channing Frye EXPOSED Kevin Love as BBQ Chicken! #nba #basketball #1v1</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>78505</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>1656</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>ESPN’s Kendrick Perkins’ Wild Take on Wemby Has The Crew Crying 😂 #basketball #nba</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>49212</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>1503</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>ESPN’s Richard Jefferson: Why the Lakers OFFICIALLY Belong to Luka Now #nba</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>34320</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>349</v>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>GROUP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>DATA SOURCE: YouTube Data API — views reflect lifetime totals at time of export</t>
         </is>
@@ -9927,9 +9960,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
+++ b/master/shows/road_trippin/data/Road_Trippin_Analytics_Tracker.xlsx
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>622195</v>
+        <v>662391</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1419833</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1159952</v>
+        <v>1681029</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1172108</v>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>1786</v>
+        <v>1820</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>5016</v>
@@ -5582,70 +5582,70 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>183000</v>
+        <v>184000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>181564</v>
+        <v>182308</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>179328</v>
+        <v>180072</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>172597</v>
+        <v>173341</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>162687</v>
+        <v>163431</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>156733</v>
+        <v>157477</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>153250</v>
+        <v>153994</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>148765</v>
+        <v>149509</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>142263</v>
+        <v>143007</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>138975</v>
+        <v>139719</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>135127</v>
+        <v>135871</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>124106</v>
+        <v>124850</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>119523</v>
+        <v>120267</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>115905</v>
+        <v>116649</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>114901</v>
+        <v>115645</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>109806</v>
+        <v>110550</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>100791</v>
+        <v>101535</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>96971</v>
+        <v>97715</v>
       </c>
       <c r="T5" s="6" t="n">
-        <v>93368</v>
+        <v>94112</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>92866</v>
+        <v>93610</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>89294</v>
+        <v>90038</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>87783</v>
+        <v>88527</v>
       </c>
     </row>
     <row r="6">
@@ -6728,55 +6728,55 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>59</v>
       </c>
       <c r="H8" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>56</v>
-      </c>
       <c r="J8" s="7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>37</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="S8" s="7" t="n">
         <v>21</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.65</v>
+        <v>0.717</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.451</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1783933</v>
+        <v>2345240</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2596957</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1786</v>
+        <v>1820</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5016</v>
@@ -9370,7 +9370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⭐ BEST OF — Oct 01 – Oct 30, 2026</t>
+          <t>⭐ BEST OF — Oct 01 – Oct 31, 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9447,10 +9447,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>88552</v>
+        <v>88610</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
@@ -9471,19 +9471,19 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>NBA Opening Night: Ant &amp; LaMelo Drop 66, Portland ROLLS &amp; Haliburton Returns</t>
+          <t>LeBron Is Coasting While Philly Keeps Winning + Can Steph Hold On Until Jimmy Returns?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>50197</v>
+        <v>62380</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>641</v>
+        <v>822</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -9504,19 +9504,19 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>Perk: Tatum &amp; Jaylen Brown NEVER Had a Real Relationship + Fred VanVleet Joins Road Trippin’</t>
+          <t>NBA Opening Night: Ant &amp; LaMelo Drop 66, Portland ROLLS &amp; Haliburton Returns</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>40831</v>
+        <v>50301</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>566</v>
+        <v>641</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
@@ -9537,19 +9537,19 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>LeBron Is Coasting While Philly Keeps Winning + Can Steph Hold On Until Jimmy Returns?</t>
+          <t>Perk: Tatum &amp; Jaylen Brown NEVER Had a Real Relationship + Fred VanVleet Joins Road Trippin’</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>38891</v>
+        <v>41530</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>34831</v>
+        <v>34901</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>553</v>
@@ -9625,10 +9625,10 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>63465</v>
+        <v>71807</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>60997</v>
+        <v>62395</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>48726</v>
+        <v>48737</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>331</v>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>27717</v>
+        <v>27860</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>198</v>
@@ -9757,10 +9757,10 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>18216</v>
+        <v>23834</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -9803,10 +9803,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1303576</v>
+        <v>1373393</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>41444</v>
+        <v>43701</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>142152</v>
+        <v>143749</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3305</v>
+        <v>3335</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>78530</v>
+        <v>78536</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>1657</v>
@@ -9902,10 +9902,10 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>50024</v>
+        <v>50395</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>34521</v>
+        <v>34611</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>350</v>
